--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="15">
   <si>
     <t>מוצר</t>
   </si>
@@ -31,16 +31,13 @@
     <t>חלב 3% תנובה 1 ליטר</t>
   </si>
   <si>
-    <t>אושר עד</t>
+    <t/>
   </si>
   <si>
     <t>קוטג' תנובה 5% 250 גרם</t>
   </si>
   <si>
     <t>טונה סטארקיסט בשמן 4X160 גרם</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
@@ -81,7 +78,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -91,16 +88,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5597"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E0B4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,28 +108,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,7 +461,7 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -513,16 +488,16 @@
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
         <v>7.35</v>
       </c>
-      <c r="D2" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -530,16 +505,16 @@
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3">
-        <v>5.9</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2">
         <v>6.4</v>
       </c>
-      <c r="D3" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -547,115 +522,119 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5">
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2">
         <v>26.9</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5" t="s">
-        <v>9</v>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3">
-        <v>35.9</v>
-      </c>
-      <c r="C5" s="4">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
         <v>39.9</v>
       </c>
-      <c r="D5" s="5">
-        <v>4</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>10.9</v>
-      </c>
-      <c r="C6" s="4">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2">
         <v>13.9</v>
       </c>
-      <c r="D6" s="5">
-        <v>3</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3">
-        <v>39.9</v>
-      </c>
-      <c r="C7" s="4">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2">
         <v>43.9</v>
       </c>
-      <c r="D7" s="5">
-        <v>4</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3">
-        <v>13.07</v>
-      </c>
-      <c r="C8" s="4">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2">
         <v>15.48</v>
       </c>
-      <c r="D8" s="5">
-        <v>2.41</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="3">
-        <v>8.2</v>
-      </c>
-      <c r="C9" s="4">
-        <v>9.5</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="7">
-        <v>121.07</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3">
         <v>163.33</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>9</v>
+      <c r="D10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>מוצר</t>
   </si>
@@ -31,15 +31,18 @@
     <t>חלב 3% תנובה 1 ליטר</t>
   </si>
   <si>
+    <t>אושר עד</t>
+  </si>
+  <si>
+    <t>קוטג' תנובה 5% 250 גרם</t>
+  </si>
+  <si>
+    <t>טונה סטארקיסט בשמן 4X160 גרם</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>קוטג' תנובה 5% 250 גרם</t>
-  </si>
-  <si>
-    <t>טונה סטארקיסט בשמן 4X160 גרם</t>
-  </si>
-  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
@@ -55,14 +58,20 @@
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
-    <t>סה"כ</t>
+    <t>סה"כ (7 מוצרים - טונה חסרה מאושר עד)</t>
+  </si>
+  <si>
+    <t>אושר עד זול יותר</t>
+  </si>
+  <si>
+    <t>הערה: טונה סטארקיסט (7290005287206) לא נמצאה בקטלוג אושר עד ב-24-25/08 - כנראה לא במלאי</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -73,12 +82,19 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <b/>
     </font>
+    <font/>
+    <font>
+      <i/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -88,6 +104,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -108,17 +139,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,16 +498,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,156 +525,159 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="C2" s="3">
+        <v>7.35</v>
+      </c>
+      <c r="D2">
+        <v>0.15</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2">
-        <v>7.35</v>
-      </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5">
+        <v>26.9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2">
+        <v>35.9</v>
+      </c>
+      <c r="C5" s="3">
+        <v>39.9</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="C6" s="3">
+        <v>13.9</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2">
-        <v>6.4</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2">
+        <v>39.9</v>
+      </c>
+      <c r="C7" s="3">
+        <v>43.9</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2">
+        <v>13.07</v>
+      </c>
+      <c r="C8" s="3">
+        <v>15.48</v>
+      </c>
+      <c r="D8">
+        <v>2.41</v>
+      </c>
+      <c r="E8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2">
+        <v>8.2</v>
+      </c>
+      <c r="C9" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="D9">
+        <v>1.3</v>
+      </c>
+      <c r="E9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2">
-        <v>26.9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2">
-        <v>39.9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2">
-        <v>13.9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2">
-        <v>43.9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2">
-        <v>15.48</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="A10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="7">
+        <v>121.07</v>
+      </c>
+      <c r="C10" s="7">
         <v>163.33</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>6</v>
+      <c r="D10" s="6">
+        <v>42.26</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>מוצר</t>
   </si>
@@ -58,20 +58,14 @@
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
-    <t>סה"כ (7 מוצרים - טונה חסרה מאושר עד)</t>
-  </si>
-  <si>
-    <t>אושר עד זול יותר</t>
-  </si>
-  <si>
-    <t>הערה: טונה סטארקיסט (7290005287206) לא נמצאה בקטלוג אושר עד ב-24-25/08 - כנראה לא במלאי</t>
+    <t>סה"כ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -82,16 +76,9 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
     </font>
     <font>
       <b/>
-    </font>
-    <font/>
-    <font>
-      <i/>
-      <color rgb="FF808080"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -139,26 +126,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,186 +501,183 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="6">
         <v>7.2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="7">
         <v>7.35</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="8">
         <v>0.15</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="6">
         <v>5.9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="7">
         <v>6.4</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="8">
         <v>0.5</v>
       </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5">
+      <c r="B4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="9">
         <v>26.9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="6">
         <v>35.9</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="7">
         <v>39.9</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="8">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="E5" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="6">
         <v>10.9</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="7">
         <v>13.9</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="8">
         <v>3</v>
       </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="E6" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="6">
         <v>39.9</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="7">
         <v>43.9</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="8">
         <v>4</v>
       </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="E7" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="6">
         <v>13.07</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="7">
         <v>15.48</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="8">
         <v>2.41</v>
       </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="E8" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="6">
         <v>8.2</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="7">
         <v>9.5</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="8">
         <v>1.3</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="11">
         <v>121.07</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="11">
         <v>163.33</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="11">
         <v>42.26</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>17</v>
+      <c r="E10" s="12" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>מוצר</t>
   </si>
@@ -40,9 +40,6 @@
     <t>טונה סטארקיסט בשמן 4X160 גרם</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
@@ -58,14 +55,26 @@
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
-    <t>סה"כ</t>
+    <t>תפוח עץ פינק ליידי 1 ק"ג</t>
+  </si>
+  <si>
+    <t>סה"כ (9 מוצרים)</t>
+  </si>
+  <si>
+    <t>אושר עד זול יותר</t>
+  </si>
+  <si>
+    <t>הערה: טונה - אושר עד מוכרים אותו מוצר (טונה בשמן סטארקיסט 4X160 גרם, ת. ישראל) תחת ברקוד שונה (7290005287213) מזה של שופרסל (7290005287206) - מותאם לפי זהות מוצר, לא ברקוד.</t>
+  </si>
+  <si>
+    <t>הערה: ביצים - אושר עד מוכרים אריזת 18 יח' בינוני (מנורמל למחיר ל-12), שופרסל אריזת 12 יח' XL - קרוב ביותר שנמצא בין שני הקמעונאים.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -76,12 +85,19 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <b/>
     </font>
+    <font/>
+    <font>
+      <i/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,11 +121,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -126,42 +137,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,183 +490,210 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="2">
         <v>7.2</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="3">
         <v>7.35</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2">
         <v>0.15</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="2">
         <v>5.9</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="3">
         <v>6.4</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3">
         <v>0.5</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="2">
+        <v>20.9</v>
+      </c>
+      <c r="C4" s="3">
+        <v>26.9</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="9">
-        <v>26.9</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="2">
+        <v>35.9</v>
+      </c>
+      <c r="C5" s="3">
+        <v>39.9</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6">
-        <v>35.9</v>
-      </c>
-      <c r="C5" s="7">
+      <c r="B6" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="C6" s="3">
+        <v>13.9</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
         <v>39.9</v>
       </c>
-      <c r="D5" s="8">
+      <c r="C7" s="3">
+        <v>43.9</v>
+      </c>
+      <c r="D7">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="6">
-        <v>10.9</v>
-      </c>
-      <c r="C6" s="7">
-        <v>13.9</v>
-      </c>
-      <c r="D6" s="8">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6">
-        <v>39.9</v>
-      </c>
-      <c r="C7" s="7">
-        <v>43.9</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="B8" s="2">
+        <v>13.07</v>
+      </c>
+      <c r="C8" s="3">
+        <v>15.48</v>
+      </c>
+      <c r="D8">
+        <v>2.41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2">
+        <v>8.2</v>
+      </c>
+      <c r="C9" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="D9">
+        <v>1.3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="C10" s="3">
+        <v>19.9</v>
+      </c>
+      <c r="D10">
         <v>4</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="6">
-        <v>13.07</v>
-      </c>
-      <c r="C8" s="7">
-        <v>15.48</v>
-      </c>
-      <c r="D8" s="8">
-        <v>2.41</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="6">
-        <v>8.2</v>
-      </c>
-      <c r="C9" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.3</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="11">
-        <v>121.07</v>
-      </c>
-      <c r="C10" s="11">
-        <v>163.33</v>
-      </c>
-      <c r="D10" s="11">
-        <v>42.26</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>6</v>
+      <c r="B11" s="5">
+        <v>157.87</v>
+      </c>
+      <c r="C11" s="5">
+        <v>183.23</v>
+      </c>
+      <c r="D11" s="4">
+        <v>25.36</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>מוצר</t>
   </si>
@@ -58,23 +58,14 @@
     <t>תפוח עץ פינק ליידי 1 ק"ג</t>
   </si>
   <si>
-    <t>סה"כ (9 מוצרים)</t>
-  </si>
-  <si>
-    <t>אושר עד זול יותר</t>
-  </si>
-  <si>
-    <t>הערה: טונה - אושר עד מוכרים אותו מוצר (טונה בשמן סטארקיסט 4X160 גרם, ת. ישראל) תחת ברקוד שונה (7290005287213) מזה של שופרסל (7290005287206) - מותאם לפי זהות מוצר, לא ברקוד.</t>
-  </si>
-  <si>
-    <t>הערה: ביצים - אושר עד מוכרים אריזת 18 יח' בינוני (מנורמל למחיר ל-12), שופרסל אריזת 12 יח' XL - קרוב ביותר שנמצא בין שני הקמעונאים.</t>
+    <t>סה"כ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -85,16 +76,9 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
     </font>
     <font>
       <b/>
-    </font>
-    <font/>
-    <font>
-      <i/>
-      <color rgb="FF808080"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -142,15 +126,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,16 +470,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +506,7 @@
       <c r="C2" s="3">
         <v>7.35</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <v>0.15</v>
       </c>
       <c r="E2" t="s">
@@ -543,7 +523,7 @@
       <c r="C3" s="3">
         <v>6.4</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>0.5</v>
       </c>
       <c r="E3" t="s">
@@ -560,7 +540,7 @@
       <c r="C4" s="3">
         <v>26.9</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>6</v>
       </c>
       <c r="E4" t="s">
@@ -577,7 +557,7 @@
       <c r="C5" s="3">
         <v>39.9</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>4</v>
       </c>
       <c r="E5" t="s">
@@ -594,7 +574,7 @@
       <c r="C6" s="3">
         <v>13.9</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>3</v>
       </c>
       <c r="E6" t="s">
@@ -611,7 +591,7 @@
       <c r="C7" s="3">
         <v>43.9</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>4</v>
       </c>
       <c r="E7" t="s">
@@ -628,7 +608,7 @@
       <c r="C8" s="3">
         <v>15.48</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>2.41</v>
       </c>
       <c r="E8" t="s">
@@ -645,7 +625,7 @@
       <c r="C9" s="3">
         <v>9.5</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>1.3</v>
       </c>
       <c r="E9" t="s">
@@ -662,7 +642,7 @@
       <c r="C10" s="3">
         <v>19.9</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>4</v>
       </c>
       <c r="E10" t="s">
@@ -670,30 +650,20 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="6">
         <v>157.87</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="6">
         <v>183.23</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="6">
         <v>25.36</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>18</v>
+      <c r="E11" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
   <si>
     <t>מוצר</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>סה"כ</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -121,16 +124,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,25 +488,25 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="2" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -500,16 +514,16 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>7.2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>7.35</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="1">
         <v>0.15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -517,16 +531,16 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="4">
         <v>5.9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>6.4</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="1">
         <v>0.5</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -534,16 +548,16 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>20.9</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>26.9</v>
       </c>
-      <c r="D4" s="4">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="1">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -551,16 +565,16 @@
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>35.9</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>39.9</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -568,16 +582,16 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>10.9</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>13.9</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="1">
         <v>3</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -585,16 +599,16 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>39.9</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>43.9</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="1">
         <v>4</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -602,16 +616,16 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <v>13.07</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>15.48</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="1">
         <v>2.41</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -619,16 +633,16 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="4">
         <v>8.2</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>9.5</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="1">
         <v>1.3</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -636,34 +650,34 @@
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="4">
         <v>15.9</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>19.9</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="1">
         <v>4</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>157.87</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>183.23</v>
       </c>
-      <c r="D11" s="6">
-        <v>25.36</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>6</v>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
   <si>
     <t>מוצר</t>
   </si>
@@ -28,12 +28,21 @@
     <t>זול יותר ב</t>
   </si>
   <si>
+    <t>שינוי אושר עד מאתמול</t>
+  </si>
+  <si>
+    <t>שינוי שופרסל מאתמול</t>
+  </si>
+  <si>
     <t>חלב 3% תנובה 1 ליטר</t>
   </si>
   <si>
     <t>אושר עד</t>
   </si>
   <si>
+    <t>ללא שינוי</t>
+  </si>
+  <si>
     <t>קוטג' תנובה 5% 250 גרם</t>
   </si>
   <si>
@@ -58,17 +67,23 @@
     <t>תפוח עץ פינק ליידי 1 ק"ג</t>
   </si>
   <si>
-    <t>סה"כ</t>
+    <t>סה"כ (9 מוצרים)</t>
+  </si>
+  <si>
+    <t>אושר עד זול יותר</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>מקרא: עמודות "שינוי" משוות את מחיר 2026-08-27 מול 2026-08-26 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -79,12 +94,19 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <b/>
     </font>
+    <font/>
+    <font>
+      <i/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -108,6 +130,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -126,25 +153,21 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,200 +507,272 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2">
         <v>7.2</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="3">
         <v>7.35</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2">
         <v>0.15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2">
+        <v>20.9</v>
+      </c>
+      <c r="C4" s="3">
+        <v>26.9</v>
+      </c>
+      <c r="D4">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4">
-        <v>5.9</v>
-      </c>
-      <c r="C3" s="5">
-        <v>6.4</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4">
-        <v>20.9</v>
-      </c>
-      <c r="C4" s="5">
-        <v>26.9</v>
-      </c>
-      <c r="D4" s="1">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="4">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2">
         <v>35.9</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <v>39.9</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="4">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2">
         <v>10.9</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
         <v>13.9</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="4">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2">
         <v>39.9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="3">
         <v>43.9</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2">
         <v>13.07</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="3">
         <v>15.48</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8">
         <v>2.41</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="4">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2">
         <v>8.2</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="3">
         <v>9.5</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>1.3</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="4">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2">
         <v>15.9</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="3">
         <v>19.9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="7">
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="6">
         <v>157.87</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>183.23</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>16</v>
+      <c r="D11" s="5">
+        <v>25.36</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>מוצר</t>
   </si>
@@ -67,7 +67,16 @@
     <t>תפוח עץ פינק ליידי 1 ק"ג</t>
   </si>
   <si>
-    <t>סה"כ (9 מוצרים)</t>
+    <t>גבינה צהובה 28% 500 גרם</t>
+  </si>
+  <si>
+    <t>שופרסל</t>
+  </si>
+  <si>
+    <t>אין נתון קודם</t>
+  </si>
+  <si>
+    <t>סה"כ (10 מוצרים)</t>
   </si>
   <si>
     <t>אושר עד זול יותר</t>
@@ -151,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -163,6 +172,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -507,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -748,19 +760,19 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="6">
-        <v>157.87</v>
-      </c>
-      <c r="C11" s="6">
-        <v>183.23</v>
-      </c>
-      <c r="D11" s="5">
-        <v>25.36</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="B11" s="3">
+        <v>29.9</v>
+      </c>
+      <c r="C11" s="2">
+        <v>26.43</v>
+      </c>
+      <c r="D11">
+        <v>3.47</v>
+      </c>
+      <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" s="5" t="s">
@@ -770,9 +782,32 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>21</v>
+      </c>
+      <c r="B12" s="7">
+        <v>187.77</v>
+      </c>
+      <c r="C12" s="7">
+        <v>209.66</v>
+      </c>
+      <c r="D12" s="6">
+        <v>21.89</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
   <si>
     <t>מוצר</t>
   </si>
@@ -67,10 +67,7 @@
     <t>תפוח עץ פינק ליידי 1 ק"ג</t>
   </si>
   <si>
-    <t>גבינה צהובה 28% 500 גרם</t>
-  </si>
-  <si>
-    <t>שופרסל</t>
+    <t>גבינה צהובה 28% (מחיר ל-100 גרם)</t>
   </si>
   <si>
     <t>אין נתון קודם</t>
@@ -763,51 +760,51 @@
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3">
-        <v>29.9</v>
-      </c>
-      <c r="C11" s="2">
-        <v>26.43</v>
+      <c r="B11" s="2">
+        <v>5.98</v>
+      </c>
+      <c r="C11" s="3">
+        <v>8.98</v>
       </c>
       <c r="D11">
-        <v>3.47</v>
+        <v>3</v>
       </c>
       <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="7">
+        <v>163.85</v>
+      </c>
+      <c r="C12" s="7">
+        <v>192.21</v>
+      </c>
+      <c r="D12" s="6">
+        <v>28.36</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="7">
-        <v>187.77</v>
-      </c>
-      <c r="C12" s="7">
-        <v>209.66</v>
-      </c>
-      <c r="D12" s="6">
-        <v>21.89</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="G12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -67,7 +67,7 @@
     <t>תפוח עץ פינק ליידי 1 ק"ג</t>
   </si>
   <si>
-    <t>גבינה צהובה 28% (מחיר ל-100 גרם)</t>
+    <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
     <t>אין נתון קודם</t>
@@ -761,13 +761,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="2">
-        <v>5.98</v>
+        <v>19.5</v>
       </c>
       <c r="C11" s="3">
-        <v>8.98</v>
+        <v>20.9</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -784,13 +784,13 @@
         <v>20</v>
       </c>
       <c r="B12" s="7">
-        <v>163.85</v>
+        <v>177.37</v>
       </c>
       <c r="C12" s="7">
-        <v>192.21</v>
+        <v>204.13</v>
       </c>
       <c r="D12" s="6">
-        <v>28.36</v>
+        <v>26.76</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>21</v>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
   <si>
     <t>מוצר</t>
   </si>
@@ -73,7 +73,25 @@
     <t>אין נתון קודם</t>
   </si>
   <si>
-    <t>סה"כ (10 מוצרים)</t>
+    <t>אקונומיקה סנו גאוול 4 ליטר</t>
+  </si>
+  <si>
+    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
+  </si>
+  <si>
+    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
+  </si>
+  <si>
+    <t>מגבוני האגיס ללא בישום 4X56</t>
+  </si>
+  <si>
+    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
+  </si>
+  <si>
+    <t>שמפו פנטן משקם 600 מ"ל</t>
+  </si>
+  <si>
+    <t>סה"כ (16 מוצרים)</t>
   </si>
   <si>
     <t>אושר עד זול יותר</t>
@@ -516,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -780,31 +798,169 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="7">
-        <v>177.37</v>
-      </c>
-      <c r="C12" s="7">
-        <v>204.13</v>
-      </c>
-      <c r="D12" s="6">
-        <v>26.76</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="B12" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="C12" s="3">
+        <v>17.9</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="B13" s="2">
+        <v>18.8</v>
+      </c>
+      <c r="C13" s="3">
+        <v>19.9</v>
+      </c>
+      <c r="D13">
+        <v>1.1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="B14" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="C14" s="3">
+        <v>18.9</v>
+      </c>
+      <c r="D14">
+        <v>4.1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>23</v>
+      </c>
+      <c r="B15" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="C15" s="3">
+        <v>24.9</v>
+      </c>
+      <c r="D15">
+        <v>5.2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="2">
+        <v>21.9</v>
+      </c>
+      <c r="C16" s="3">
+        <v>26.9</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="2">
+        <v>18.9</v>
+      </c>
+      <c r="C17" s="3">
+        <v>22.9</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="7">
+        <v>287.37</v>
+      </c>
+      <c r="C18" s="7">
+        <v>335.53</v>
+      </c>
+      <c r="D18" s="6">
+        <v>48.16</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="31">
   <si>
     <t>מוצר</t>
   </si>
@@ -91,7 +91,10 @@
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
-    <t>סה"כ (16 מוצרים)</t>
+    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
+  </si>
+  <si>
+    <t>סה"כ (17 מוצרים)</t>
   </si>
   <si>
     <t>אושר עד זול יותר</t>
@@ -534,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -936,31 +939,54 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="7">
-        <v>287.37</v>
-      </c>
-      <c r="C18" s="7">
-        <v>335.53</v>
-      </c>
-      <c r="D18" s="6">
-        <v>48.16</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="B18" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>48.9</v>
+      </c>
+      <c r="D18">
+        <v>7.4</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="B19" s="7">
+        <v>328.87</v>
+      </c>
+      <c r="C19" s="7">
+        <v>384.43</v>
+      </c>
+      <c r="D19" s="6">
+        <v>55.56</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="F19" s="6" t="s">
         <v>29</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="35">
   <si>
     <t>מוצר</t>
   </si>
@@ -94,7 +94,19 @@
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
-    <t>סה"כ (17 מוצרים)</t>
+    <t>עגבניה (ק"ג)</t>
+  </si>
+  <si>
+    <t>מלפפון (ק"ג)</t>
+  </si>
+  <si>
+    <t>בננות (ק"ג)</t>
+  </si>
+  <si>
+    <t>בצל יבש (ק"ג)</t>
+  </si>
+  <si>
+    <t>סה"כ (21 מוצרים)</t>
   </si>
   <si>
     <t>אושר עד זול יותר</t>
@@ -537,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -962,31 +974,123 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="7">
-        <v>328.87</v>
-      </c>
-      <c r="C19" s="7">
-        <v>384.43</v>
-      </c>
-      <c r="D19" s="6">
-        <v>55.56</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="B19" s="2">
+        <v>4.9</v>
+      </c>
+      <c r="C19" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="B20" s="2">
+        <v>4.9</v>
+      </c>
+      <c r="C20" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="B21" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="C21" s="3">
+        <v>12.9</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>30</v>
+      </c>
+      <c r="B22" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="C22" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="7">
+        <v>352.47</v>
+      </c>
+      <c r="C23" s="7">
+        <v>421.03</v>
+      </c>
+      <c r="D23" s="6">
+        <v>68.56</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="38">
   <si>
     <t>מוצר</t>
   </si>
@@ -106,7 +106,16 @@
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
-    <t>סה"כ (21 מוצרים)</t>
+    <t>סירופ יכין פטל דיאט 1 ליטר</t>
+  </si>
+  <si>
+    <t>יין סגל אדום יבש 750 מ"ל</t>
+  </si>
+  <si>
+    <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
+  </si>
+  <si>
+    <t>סה"כ (24 מוצרים)</t>
   </si>
   <si>
     <t>אושר עד זול יותר</t>
@@ -549,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -1066,31 +1075,100 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="7">
-        <v>352.47</v>
-      </c>
-      <c r="C23" s="7">
-        <v>421.03</v>
-      </c>
-      <c r="D23" s="6">
-        <v>68.56</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="B23" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="C23" s="3">
+        <v>13.9</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="B24" s="2">
+        <v>19.9</v>
+      </c>
+      <c r="C24" s="3">
+        <v>24.9</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="B25" s="2">
+        <v>42.9</v>
+      </c>
+      <c r="C25" s="3">
+        <v>45.9</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>34</v>
+      </c>
+      <c r="B26" s="7">
+        <v>425.17</v>
+      </c>
+      <c r="C26" s="7">
+        <v>505.73</v>
+      </c>
+      <c r="D26" s="6">
+        <v>80.56</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="42">
   <si>
     <t>מוצר</t>
   </si>
@@ -34,6 +34,9 @@
     <t>שינוי שופרסל מאתמול</t>
   </si>
   <si>
+    <t>מוצרי חלב</t>
+  </si>
+  <si>
     <t>חלב 3% תנובה 1 ליטר</t>
   </si>
   <si>
@@ -46,54 +49,72 @@
     <t>קוטג' תנובה 5% 250 גרם</t>
   </si>
   <si>
+    <t>גבינה צהובה 9% פרוסות 200 גרם</t>
+  </si>
+  <si>
+    <t>אין נתון קודם</t>
+  </si>
+  <si>
+    <t>מאכל ושתיה סגורים</t>
+  </si>
+  <si>
     <t>טונה סטארקיסט בשמן 4X160 גרם</t>
   </si>
   <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
+    <t>ביצים L (מנורמל ל-12 יח')</t>
+  </si>
+  <si>
+    <t>קוקה קולה זירו 1.5 ליטר</t>
+  </si>
+  <si>
+    <t>סירופ יכין פטל דיאט 1 ליטר</t>
+  </si>
+  <si>
+    <t>יין סגל אדום יבש 750 מ"ל</t>
+  </si>
+  <si>
+    <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
+  </si>
+  <si>
+    <t>ניקיון וטואלטיקה</t>
+  </si>
+  <si>
     <t>מגבות נייר ניקול 6 גלילים</t>
   </si>
   <si>
     <t>נייר טואלט לילי פסטל 32 גלילים</t>
   </si>
   <si>
-    <t>ביצים L (מנורמל ל-12 יח')</t>
-  </si>
-  <si>
-    <t>קוקה קולה זירו 1.5 ליטר</t>
+    <t>אקונומיקה סנו גאוול 4 ליטר</t>
+  </si>
+  <si>
+    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
+  </si>
+  <si>
+    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
+  </si>
+  <si>
+    <t>מגבוני האגיס ללא בישום 4X56</t>
+  </si>
+  <si>
+    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
+  </si>
+  <si>
+    <t>שמפו פנטן משקם 600 מ"ל</t>
+  </si>
+  <si>
+    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
+  </si>
+  <si>
+    <t>פירות וירקות</t>
   </si>
   <si>
     <t>תפוח עץ פינק ליידי 1 ק"ג</t>
   </si>
   <si>
-    <t>גבינה צהובה 9% פרוסות 200 גרם</t>
-  </si>
-  <si>
-    <t>אין נתון קודם</t>
-  </si>
-  <si>
-    <t>אקונומיקה סנו גאוול 4 ליטר</t>
-  </si>
-  <si>
-    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
-  </si>
-  <si>
-    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
-  </si>
-  <si>
-    <t>מגבוני האגיס ללא בישום 4X56</t>
-  </si>
-  <si>
-    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
-  </si>
-  <si>
-    <t>שמפו פנטן משקם 600 מ"ל</t>
-  </si>
-  <si>
-    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
-  </si>
-  <si>
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
@@ -104,15 +125,6 @@
   </si>
   <si>
     <t>בצל יבש (ק"ג)</t>
-  </si>
-  <si>
-    <t>סירופ יכין פטל דיאט 1 ליטר</t>
-  </si>
-  <si>
-    <t>יין סגל אדום יבש 750 מ"ל</t>
-  </si>
-  <si>
-    <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
     <t>סה"כ (24 מוצרים)</t>
@@ -131,7 +143,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -146,6 +158,10 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
     </font>
     <font/>
     <font>
@@ -154,7 +170,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,6 +180,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -199,26 +220,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,10 +582,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -591,587 +615,637 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2">
-        <v>7.2</v>
-      </c>
-      <c r="C2" s="3">
-        <v>7.35</v>
-      </c>
-      <c r="D2">
-        <v>0.15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2">
-        <v>5.9</v>
-      </c>
-      <c r="C3" s="3">
-        <v>6.4</v>
+        <v>8</v>
+      </c>
+      <c r="B3" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>7.35</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2">
-        <v>20.9</v>
-      </c>
-      <c r="C4" s="3">
-        <v>26.9</v>
+      <c r="B4" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="C4" s="4">
+        <v>6.4</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2">
-        <v>35.9</v>
-      </c>
-      <c r="C5" s="3">
-        <v>39.9</v>
+      <c r="B5" s="3">
+        <v>19.5</v>
+      </c>
+      <c r="C5" s="4">
+        <v>20.9</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2">
-        <v>10.9</v>
-      </c>
-      <c r="C6" s="3">
-        <v>13.9</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2">
-        <v>39.9</v>
-      </c>
-      <c r="C7" s="3">
-        <v>43.9</v>
+        <v>15</v>
+      </c>
+      <c r="B7" s="3">
+        <v>20.9</v>
+      </c>
+      <c r="C7" s="4">
+        <v>26.9</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="2">
-        <v>13.07</v>
-      </c>
-      <c r="C8" s="3">
-        <v>15.48</v>
+        <v>16</v>
+      </c>
+      <c r="B8" s="3">
+        <v>35.9</v>
+      </c>
+      <c r="C8" s="4">
+        <v>39.9</v>
       </c>
       <c r="D8">
-        <v>2.41</v>
+        <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2">
-        <v>8.2</v>
-      </c>
-      <c r="C9" s="3">
-        <v>9.5</v>
+        <v>17</v>
+      </c>
+      <c r="B9" s="3">
+        <v>13.07</v>
+      </c>
+      <c r="C9" s="4">
+        <v>15.48</v>
       </c>
       <c r="D9">
-        <v>1.3</v>
+        <v>2.41</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="2">
-        <v>15.9</v>
-      </c>
-      <c r="C10" s="3">
-        <v>19.9</v>
+        <v>18</v>
+      </c>
+      <c r="B10" s="3">
+        <v>8.2</v>
+      </c>
+      <c r="C10" s="4">
+        <v>9.5</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2">
-        <v>19.5</v>
-      </c>
-      <c r="C11" s="3">
-        <v>20.9</v>
+        <v>19</v>
+      </c>
+      <c r="B11" s="3">
+        <v>9.9</v>
+      </c>
+      <c r="C11" s="4">
+        <v>13.9</v>
       </c>
       <c r="D11">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="2">
-        <v>15.9</v>
-      </c>
-      <c r="C12" s="3">
-        <v>17.9</v>
+      <c r="B12" s="3">
+        <v>19.9</v>
+      </c>
+      <c r="C12" s="4">
+        <v>24.9</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="2">
-        <v>18.8</v>
-      </c>
-      <c r="C13" s="3">
-        <v>19.9</v>
+      <c r="B13" s="3">
+        <v>42.9</v>
+      </c>
+      <c r="C13" s="4">
+        <v>45.9</v>
       </c>
       <c r="D13">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="2">
-        <v>14.8</v>
-      </c>
-      <c r="C14" s="3">
-        <v>18.9</v>
-      </c>
-      <c r="D14">
-        <v>4.1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="2">
-        <v>19.7</v>
-      </c>
-      <c r="C15" s="3">
-        <v>24.9</v>
+      <c r="B15" s="3">
+        <v>10.9</v>
+      </c>
+      <c r="C15" s="4">
+        <v>13.9</v>
       </c>
       <c r="D15">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="2">
-        <v>21.9</v>
-      </c>
-      <c r="C16" s="3">
-        <v>26.9</v>
+      <c r="B16" s="3">
+        <v>39.9</v>
+      </c>
+      <c r="C16" s="4">
+        <v>43.9</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="2">
-        <v>18.9</v>
-      </c>
-      <c r="C17" s="3">
-        <v>22.9</v>
+      <c r="B17" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="C17" s="4">
+        <v>17.9</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="2">
-        <v>41.5</v>
-      </c>
-      <c r="C18" s="3">
-        <v>48.9</v>
+      <c r="B18" s="3">
+        <v>18.8</v>
+      </c>
+      <c r="C18" s="4">
+        <v>19.9</v>
       </c>
       <c r="D18">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="2">
-        <v>4.9</v>
-      </c>
-      <c r="C19" s="3">
-        <v>8.9</v>
+      <c r="B19" s="3">
+        <v>14.8</v>
+      </c>
+      <c r="C19" s="4">
+        <v>18.9</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="2">
-        <v>4.9</v>
-      </c>
-      <c r="C20" s="3">
-        <v>8.9</v>
+      <c r="B20" s="3">
+        <v>19.7</v>
+      </c>
+      <c r="C20" s="4">
+        <v>24.9</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="2">
-        <v>9.9</v>
-      </c>
-      <c r="C21" s="3">
-        <v>12.9</v>
+      <c r="B21" s="3">
+        <v>21.9</v>
+      </c>
+      <c r="C21" s="4">
+        <v>26.9</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="2">
-        <v>3.9</v>
-      </c>
-      <c r="C22" s="3">
-        <v>5.9</v>
+      <c r="B22" s="3">
+        <v>18.9</v>
+      </c>
+      <c r="C22" s="4">
+        <v>22.9</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="2">
-        <v>9.9</v>
-      </c>
-      <c r="C23" s="3">
-        <v>13.9</v>
+      <c r="B23" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="C23" s="4">
+        <v>48.9</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="2">
-        <v>19.9</v>
-      </c>
-      <c r="C24" s="3">
-        <v>24.9</v>
-      </c>
-      <c r="D24">
-        <v>5</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="2">
-        <v>42.9</v>
-      </c>
-      <c r="C25" s="3">
-        <v>45.9</v>
+      <c r="B25" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="C25" s="4">
+        <v>19.9</v>
       </c>
       <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="3">
+        <v>4.9</v>
+      </c>
+      <c r="C26" s="4">
+        <v>8.9</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="3">
+        <v>4.9</v>
+      </c>
+      <c r="C27" s="4">
+        <v>8.9</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="3">
+        <v>9.9</v>
+      </c>
+      <c r="C28" s="4">
+        <v>12.9</v>
+      </c>
+      <c r="D28">
         <v>3</v>
       </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="7">
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="C29" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="8">
         <v>425.17</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C30" s="8">
         <v>505.73</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D30" s="7">
         <v>80.56</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>37</v>
+      <c r="E30" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A24:G24"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="66">
   <si>
     <t>מוצר</t>
   </si>
@@ -25,6 +25,9 @@
     <t>הפרש ₪</t>
   </si>
   <si>
+    <t>הפרש %</t>
+  </si>
+  <si>
     <t>זול יותר ב</t>
   </si>
   <si>
@@ -40,6 +43,9 @@
     <t>חלב 3% תנובה 1 ליטר</t>
   </si>
   <si>
+    <t>2.0%</t>
+  </si>
+  <si>
     <t>אושר עד</t>
   </si>
   <si>
@@ -49,9 +55,15 @@
     <t>קוטג' תנובה 5% 250 גרם</t>
   </si>
   <si>
+    <t>7.8%</t>
+  </si>
+  <si>
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
+    <t>6.7%</t>
+  </si>
+  <si>
     <t>אין נתון קודם</t>
   </si>
   <si>
@@ -61,54 +73,102 @@
     <t>טונה סטארקיסט בשמן 4X160 גרם</t>
   </si>
   <si>
+    <t>22.3%</t>
+  </si>
+  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
+    <t>10.0%</t>
+  </si>
+  <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
+    <t>15.6%</t>
+  </si>
+  <si>
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
+    <t>13.7%</t>
+  </si>
+  <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
+    <t>28.8%</t>
+  </si>
+  <si>
     <t>יין סגל אדום יבש 750 מ"ל</t>
   </si>
   <si>
+    <t>20.1%</t>
+  </si>
+  <si>
     <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
+    <t>6.5%</t>
+  </si>
+  <si>
     <t>ניקיון וטואלטיקה</t>
   </si>
   <si>
     <t>מגבות נייר ניקול 6 גלילים</t>
   </si>
   <si>
+    <t>21.6%</t>
+  </si>
+  <si>
     <t>נייר טואלט לילי פסטל 32 גלילים</t>
   </si>
   <si>
+    <t>9.1%</t>
+  </si>
+  <si>
     <t>אקונומיקה סנו גאוול 4 ליטר</t>
   </si>
   <si>
+    <t>11.2%</t>
+  </si>
+  <si>
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
   </si>
   <si>
+    <t>5.5%</t>
+  </si>
+  <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
+    <t>21.7%</t>
+  </si>
+  <si>
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
+    <t>20.9%</t>
+  </si>
+  <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
+    <t>18.6%</t>
+  </si>
+  <si>
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
+    <t>17.5%</t>
+  </si>
+  <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
+    <t>15.1%</t>
+  </si>
+  <si>
     <t>פירות וירקות</t>
   </si>
   <si>
@@ -118,16 +178,28 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
+    <t>44.9%</t>
+  </si>
+  <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
     <t>בננות (ק"ג)</t>
   </si>
   <si>
+    <t>23.3%</t>
+  </si>
+  <si>
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
+    <t>33.9%</t>
+  </si>
+  <si>
     <t>סה"כ (24 מוצרים)</t>
+  </si>
+  <si>
+    <t>15.9%</t>
   </si>
   <si>
     <t>אושר עד זול יותר</t>
@@ -234,10 +306,10 @@
     <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -582,17 +654,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="7" width="20" customWidth="1"/>
+    <col min="4" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -614,10 +686,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -625,10 +700,11 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3">
         <v>7.2</v>
@@ -639,19 +715,22 @@
       <c r="D3">
         <v>0.15</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="3">
         <v>5.9</v>
@@ -662,19 +741,22 @@
       <c r="D4">
         <v>0.5</v>
       </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3">
         <v>19.5</v>
@@ -685,19 +767,22 @@
       <c r="D5">
         <v>1.4</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -705,10 +790,11 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3">
         <v>20.9</v>
@@ -719,19 +805,22 @@
       <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B8" s="3">
         <v>35.9</v>
@@ -742,19 +831,22 @@
       <c r="D8">
         <v>4</v>
       </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B9" s="3">
         <v>13.07</v>
@@ -765,19 +857,22 @@
       <c r="D9">
         <v>2.41</v>
       </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B10" s="3">
         <v>8.2</v>
@@ -788,19 +883,22 @@
       <c r="D10">
         <v>1.3</v>
       </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B11" s="3">
         <v>9.9</v>
@@ -811,19 +909,22 @@
       <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B12" s="3">
         <v>19.9</v>
@@ -834,19 +935,22 @@
       <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>42.9</v>
@@ -857,19 +961,22 @@
       <c r="D13">
         <v>3</v>
       </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -877,10 +984,11 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3">
         <v>10.9</v>
@@ -891,19 +999,22 @@
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3">
         <v>39.9</v>
@@ -914,19 +1025,22 @@
       <c r="D16">
         <v>4</v>
       </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3">
         <v>15.9</v>
@@ -937,19 +1051,22 @@
       <c r="D17">
         <v>2</v>
       </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B18" s="3">
         <v>18.8</v>
@@ -960,19 +1077,22 @@
       <c r="D18">
         <v>1.1</v>
       </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B19" s="3">
         <v>14.8</v>
@@ -983,19 +1103,22 @@
       <c r="D19">
         <v>4.1</v>
       </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E19" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B20" s="3">
         <v>19.7</v>
@@ -1006,19 +1129,22 @@
       <c r="D20">
         <v>5.2</v>
       </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B21" s="3">
         <v>21.9</v>
@@ -1029,19 +1155,22 @@
       <c r="D21">
         <v>5</v>
       </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B22" s="3">
         <v>18.9</v>
@@ -1052,19 +1181,22 @@
       <c r="D22">
         <v>4</v>
       </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B23" s="3">
         <v>41.5</v>
@@ -1075,19 +1207,22 @@
       <c r="D23">
         <v>7.4</v>
       </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E23" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1095,10 +1230,11 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="B25" s="3">
         <v>15.9</v>
@@ -1109,19 +1245,22 @@
       <c r="D25">
         <v>4</v>
       </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B26" s="3">
         <v>4.9</v>
@@ -1132,19 +1271,22 @@
       <c r="D26">
         <v>4</v>
       </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B27" s="3">
         <v>4.9</v>
@@ -1155,19 +1297,22 @@
       <c r="D27">
         <v>4</v>
       </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E27" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B28" s="3">
         <v>9.9</v>
@@ -1178,19 +1323,22 @@
       <c r="D28">
         <v>3</v>
       </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B29" s="3">
         <v>3.9</v>
@@ -1201,19 +1349,22 @@
       <c r="D29">
         <v>2</v>
       </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E29" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="B30" s="8">
         <v>425.17</v>
@@ -1225,26 +1376,29 @@
         <v>80.56</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>40</v>
+        <v>64</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A24:H24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="64">
   <si>
     <t>מוצר</t>
   </si>
@@ -64,9 +64,6 @@
     <t>6.7%</t>
   </si>
   <si>
-    <t>אין נתון קודם</t>
-  </si>
-  <si>
     <t>מאכל ושתיה סגורים</t>
   </si>
   <si>
@@ -196,26 +193,23 @@
     <t>33.9%</t>
   </si>
   <si>
-    <t>סה"כ (24 מוצרים)</t>
+    <t>סה"כ</t>
   </si>
   <si>
     <t>15.9%</t>
   </si>
   <si>
-    <t>אושר עד זול יותר</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>מקרא: עמודות "שינוי" משוות את מחיר 2026-08-27 מול 2026-08-26 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-08-28 מול 2026-08-27 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -226,19 +220,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
     </font>
     <font>
       <b/>
     </font>
-    <font/>
     <font>
       <i/>
-      <color rgb="FF808080"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -292,29 +279,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -654,17 +633,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="2" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -715,16 +691,16 @@
       <c r="D3">
         <v>0.15</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -741,16 +717,16 @@
       <c r="D4">
         <v>0.5</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -767,22 +743,22 @@
       <c r="D5">
         <v>1.4</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -794,7 +770,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3">
         <v>20.9</v>
@@ -805,22 +781,22 @@
       <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>20</v>
+      <c r="E7" t="s">
+        <v>19</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="6" t="s">
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="3">
         <v>35.9</v>
@@ -831,22 +807,22 @@
       <c r="D8">
         <v>4</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>22</v>
+      <c r="E8" t="s">
+        <v>21</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="6" t="s">
+      <c r="G8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="3">
         <v>13.07</v>
@@ -857,22 +833,22 @@
       <c r="D9">
         <v>2.41</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>24</v>
+      <c r="E9" t="s">
+        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="6" t="s">
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3">
         <v>8.2</v>
@@ -883,22 +859,22 @@
       <c r="D10">
         <v>1.3</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>26</v>
+      <c r="E10" t="s">
+        <v>25</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="6" t="s">
+      <c r="G10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="3">
         <v>9.9</v>
@@ -909,22 +885,22 @@
       <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>28</v>
+      <c r="E11" t="s">
+        <v>27</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="3">
         <v>19.9</v>
@@ -935,22 +911,22 @@
       <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>30</v>
+      <c r="E12" t="s">
+        <v>29</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="3">
         <v>42.9</v>
@@ -961,22 +937,22 @@
       <c r="D13">
         <v>3</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -988,7 +964,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3">
         <v>10.9</v>
@@ -999,22 +975,22 @@
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>35</v>
+      <c r="E15" t="s">
+        <v>34</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="6" t="s">
+      <c r="G15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3">
         <v>39.9</v>
@@ -1025,22 +1001,22 @@
       <c r="D16">
         <v>4</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>37</v>
+      <c r="E16" t="s">
+        <v>36</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="6" t="s">
+      <c r="G16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3">
         <v>15.9</v>
@@ -1051,22 +1027,22 @@
       <c r="D17">
         <v>2</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>39</v>
+      <c r="E17" t="s">
+        <v>38</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="3">
         <v>18.8</v>
@@ -1077,22 +1053,22 @@
       <c r="D18">
         <v>1.1</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>41</v>
+      <c r="E18" t="s">
+        <v>40</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="3">
         <v>14.8</v>
@@ -1103,22 +1079,22 @@
       <c r="D19">
         <v>4.1</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>43</v>
+      <c r="E19" t="s">
+        <v>42</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="3">
         <v>19.7</v>
@@ -1129,22 +1105,22 @@
       <c r="D20">
         <v>5.2</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>45</v>
+      <c r="E20" t="s">
+        <v>44</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="3">
         <v>21.9</v>
@@ -1155,22 +1131,22 @@
       <c r="D21">
         <v>5</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>47</v>
+      <c r="E21" t="s">
+        <v>46</v>
       </c>
       <c r="F21" t="s">
         <v>11</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="3">
         <v>18.9</v>
@@ -1181,22 +1157,22 @@
       <c r="D22">
         <v>4</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>49</v>
+      <c r="E22" t="s">
+        <v>48</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" s="3">
         <v>41.5</v>
@@ -1207,22 +1183,22 @@
       <c r="D23">
         <v>7.4</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1234,7 +1210,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3">
         <v>15.9</v>
@@ -1245,22 +1221,22 @@
       <c r="D25">
         <v>4</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>30</v>
+      <c r="E25" t="s">
+        <v>29</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" s="6" t="s">
+      <c r="G25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" s="3">
         <v>4.9</v>
@@ -1271,22 +1247,22 @@
       <c r="D26">
         <v>4</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>55</v>
+      <c r="E26" t="s">
+        <v>54</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B27" s="3">
         <v>4.9</v>
@@ -1297,22 +1273,22 @@
       <c r="D27">
         <v>4</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>55</v>
+      <c r="E27" t="s">
+        <v>54</v>
       </c>
       <c r="F27" t="s">
         <v>11</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="3">
         <v>9.9</v>
@@ -1323,22 +1299,22 @@
       <c r="D28">
         <v>3</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>58</v>
+      <c r="E28" t="s">
+        <v>57</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" s="3">
         <v>3.9</v>
@@ -1349,56 +1325,64 @@
       <c r="D29">
         <v>2</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="B30" s="6">
+        <v>425.17</v>
+      </c>
+      <c r="C30" s="6">
+        <v>505.73</v>
+      </c>
+      <c r="D30" s="6">
+        <v>80.56</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="8">
-        <v>425.17</v>
-      </c>
-      <c r="C30" s="8">
-        <v>505.73</v>
-      </c>
-      <c r="D30" s="7">
-        <v>80.56</v>
-      </c>
-      <c r="E30" s="7" t="s">
+      <c r="F30" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="G30" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>65</v>
-      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -202,7 +202,7 @@
     <t/>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-08-28 מול 2026-08-27 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-08-29 מול 2026-08-28 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
   </si>
 </sst>
 </file>
@@ -279,18 +279,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -636,8 +647,11 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="8" width="22" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -678,81 +692,81 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>7.2</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>7.35</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>0.15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>5.9</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>6.4</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>0.5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>19.5</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>20.9</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>1.4</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -768,185 +782,185 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>20.9</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>26.9</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>6</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="F7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>35.9</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>39.9</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>4</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="F8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>13.07</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>15.48</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="3">
         <v>2.41</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="F9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>8.2</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>9.5</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="3">
         <v>1.3</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="F10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>9.9</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>13.9</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="3">
         <v>4</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="F11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>19.9</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>24.9</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <v>5</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="F12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>42.9</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>45.9</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="3">
         <v>3</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="F13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -962,237 +976,237 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>10.9</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>13.9</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="3">
         <v>3</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="F15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>39.9</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>43.9</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="3">
         <v>4</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="F16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>15.9</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>17.9</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="3">
         <v>2</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="F17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>18.8</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <v>19.9</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="3">
         <v>1.1</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="F18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>14.8</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>18.9</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="3">
         <v>4.1</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="F19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>19.7</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>24.9</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="3">
         <v>5.2</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="F20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>21.9</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>26.9</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="3">
         <v>5</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="F21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>18.9</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>22.9</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="3">
         <v>4</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="F22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>41.5</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>48.9</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="3">
         <v>7.4</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="F23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1208,173 +1222,173 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>15.9</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <v>19.9</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="3">
         <v>4</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="F25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>4.9</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
         <v>8.9</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="3">
         <v>4</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="F26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="4">
         <v>4.9</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <v>8.9</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="3">
         <v>4</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F27" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="F27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>9.9</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <v>12.9</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="3">
         <v>3</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F28" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="F28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="4">
         <v>3.9</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>5.9</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="3">
         <v>2</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="5" t="s">
+      <c r="F29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="7">
         <v>425.17</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="7">
         <v>505.73</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="7">
         <v>80.56</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="79">
   <si>
     <t>מוצר</t>
   </si>
@@ -46,7 +46,7 @@
     <t>2.0%</t>
   </si>
   <si>
-    <t>אושר עד</t>
+    <t>אושר עד (0.15 ₪)</t>
   </si>
   <si>
     <t>ללא שינוי</t>
@@ -58,12 +58,18 @@
     <t>7.8%</t>
   </si>
   <si>
+    <t>אושר עד (0.50 ₪)</t>
+  </si>
+  <si>
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
     <t>6.7%</t>
   </si>
   <si>
+    <t>אושר עד (1.40 ₪)</t>
+  </si>
+  <si>
     <t>מאכל ושתיה סגורים</t>
   </si>
   <si>
@@ -73,24 +79,36 @@
     <t>22.3%</t>
   </si>
   <si>
+    <t>אושר עד (6.00 ₪)</t>
+  </si>
+  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
     <t>10.0%</t>
   </si>
   <si>
+    <t>אושר עד (4.00 ₪)</t>
+  </si>
+  <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
     <t>15.6%</t>
   </si>
   <si>
+    <t>אושר עד (2.41 ₪)</t>
+  </si>
+  <si>
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
     <t>13.7%</t>
   </si>
   <si>
+    <t>אושר עד (1.30 ₪)</t>
+  </si>
+  <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
@@ -103,12 +121,18 @@
     <t>20.1%</t>
   </si>
   <si>
+    <t>אושר עד (5.00 ₪)</t>
+  </si>
+  <si>
     <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
     <t>6.5%</t>
   </si>
   <si>
+    <t>אושר עד (3.00 ₪)</t>
+  </si>
+  <si>
     <t>ניקיון וטואלטיקה</t>
   </si>
   <si>
@@ -130,24 +154,36 @@
     <t>11.2%</t>
   </si>
   <si>
+    <t>אושר עד (2.00 ₪)</t>
+  </si>
+  <si>
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
   </si>
   <si>
     <t>5.5%</t>
   </si>
   <si>
+    <t>אושר עד (1.10 ₪)</t>
+  </si>
+  <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
     <t>21.7%</t>
   </si>
   <si>
+    <t>אושר עד (4.10 ₪)</t>
+  </si>
+  <si>
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
     <t>20.9%</t>
   </si>
   <si>
+    <t>אושר עד (5.20 ₪)</t>
+  </si>
+  <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
@@ -157,7 +193,7 @@
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
-    <t>17.5%</t>
+    <t/>
   </si>
   <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
@@ -166,6 +202,9 @@
     <t>15.1%</t>
   </si>
   <si>
+    <t>אושר עד (7.40 ₪)</t>
+  </si>
+  <si>
     <t>פירות וירקות</t>
   </si>
   <si>
@@ -175,19 +214,16 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
-    <t>33.7%</t>
-  </si>
-  <si>
-    <t>⬆ +1.00 ₪</t>
+    <t>44.9%</t>
+  </si>
+  <si>
+    <t>⬇ -1.00 ₪</t>
   </si>
   <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
-    <t>22.5%</t>
-  </si>
-  <si>
-    <t>⬆ +2.00 ₪</t>
+    <t>⬇ -2.00 ₪</t>
   </si>
   <si>
     <t>בננות (ק"ג)</t>
@@ -199,16 +235,19 @@
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
-    <t>16.9%</t>
+    <t>33.9%</t>
   </si>
   <si>
     <t>סה"כ</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>מקרא: עמודת 'שינוי אושר עד מאתמול' משווה את מחיר 2026-08-31 מול 2026-08-29 (אושר עד לא פרסם מחירים ב-2026-08-30, לכן ההשוואה מול התאריך התקף האחרון); עמודת 'שינוי שופרסל מאתמול' משווה מול 2026-08-30. אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
+    <t>19.7%</t>
+  </si>
+  <si>
+    <t>אושר עד (99.46 ₪)</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-01 מול 2026-08-31 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
   </si>
 </sst>
 </file>
@@ -232,10 +271,10 @@
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,7 +308,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -299,26 +343,32 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -661,17 +711,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+    <col min="7" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -755,7 +800,7 @@
         <v>14</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>12</v>
@@ -766,7 +811,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="4">
         <v>19.5</v>
@@ -778,10 +823,10 @@
         <v>1.4</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>12</v>
@@ -792,7 +837,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -804,7 +849,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="4">
         <v>20.9</v>
@@ -816,10 +861,10 @@
         <v>6</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>12</v>
@@ -830,7 +875,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4">
         <v>35.9</v>
@@ -842,10 +887,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>12</v>
@@ -856,7 +901,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B9" s="4">
         <v>13.07</v>
@@ -868,10 +913,10 @@
         <v>2.41</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>12</v>
@@ -882,7 +927,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B10" s="4">
         <v>8.2</v>
@@ -894,10 +939,10 @@
         <v>1.3</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>12</v>
@@ -908,7 +953,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4">
         <v>9.9</v>
@@ -920,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>12</v>
@@ -934,7 +979,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4">
         <v>19.9</v>
@@ -946,10 +991,10 @@
         <v>5</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>12</v>
@@ -960,7 +1005,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B13" s="4">
         <v>42.9</v>
@@ -972,10 +1017,10 @@
         <v>3</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>12</v>
@@ -986,7 +1031,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -998,7 +1043,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B15" s="4">
         <v>10.9</v>
@@ -1010,10 +1055,10 @@
         <v>3</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>12</v>
@@ -1024,7 +1069,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B16" s="4">
         <v>39.9</v>
@@ -1036,10 +1081,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>12</v>
@@ -1050,7 +1095,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" s="4">
         <v>15.9</v>
@@ -1062,10 +1107,10 @@
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>12</v>
@@ -1076,7 +1121,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B18" s="4">
         <v>18.8</v>
@@ -1088,10 +1133,10 @@
         <v>1.1</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>12</v>
@@ -1102,7 +1147,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B19" s="4">
         <v>14.8</v>
@@ -1114,10 +1159,10 @@
         <v>4.1</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>12</v>
@@ -1128,7 +1173,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B20" s="4">
         <v>19.7</v>
@@ -1140,10 +1185,10 @@
         <v>5.2</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>12</v>
@@ -1154,7 +1199,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B21" s="4">
         <v>21.9</v>
@@ -1166,10 +1211,10 @@
         <v>5</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>12</v>
@@ -1180,25 +1225,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="4">
-        <v>18.9</v>
-      </c>
-      <c r="C22" s="5">
+        <v>59</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="8">
         <v>22.9</v>
       </c>
-      <c r="D22" s="6">
-        <v>4</v>
+      <c r="D22" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>12</v>
+        <v>60</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>12</v>
@@ -1206,7 +1251,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B23" s="4">
         <v>41.5</v>
@@ -1218,10 +1263,10 @@
         <v>7.4</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>12</v>
@@ -1232,7 +1277,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1244,7 +1289,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B25" s="4">
         <v>15.9</v>
@@ -1256,10 +1301,10 @@
         <v>4</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>12</v>
@@ -1270,25 +1315,25 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B26" s="4">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="C26" s="5">
         <v>8.9</v>
       </c>
       <c r="D26" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>55</v>
+        <v>25</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>12</v>
@@ -1296,25 +1341,25 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B27" s="4">
-        <v>6.9</v>
+        <v>4.9</v>
       </c>
       <c r="C27" s="5">
         <v>8.9</v>
       </c>
       <c r="D27" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>58</v>
+        <v>25</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>12</v>
@@ -1322,7 +1367,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B28" s="4">
         <v>9.9</v>
@@ -1334,10 +1379,10 @@
         <v>3</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>12</v>
@@ -1348,67 +1393,67 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B29" s="4">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="C29" s="5">
         <v>5.9</v>
       </c>
       <c r="D29" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>55</v>
+        <v>47</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="10">
-        <v>429.17</v>
-      </c>
-      <c r="C30" s="10">
+      <c r="A30" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="11">
+        <v>406.27</v>
+      </c>
+      <c r="C30" s="11">
         <v>505.73</v>
       </c>
-      <c r="D30" s="10">
-        <v>76.56</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>64</v>
+      <c r="D30" s="11">
+        <v>99.46</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1416,7 +1461,7 @@
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A32:H32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="77">
   <si>
     <t>מוצר</t>
   </si>
@@ -217,15 +217,9 @@
     <t>44.9%</t>
   </si>
   <si>
-    <t>⬇ -1.00 ₪</t>
-  </si>
-  <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
-    <t>⬇ -2.00 ₪</t>
-  </si>
-  <si>
     <t>בננות (ק"ג)</t>
   </si>
   <si>
@@ -247,7 +241,7 @@
     <t>אושר עד (99.46 ₪)</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-01 מול 2026-08-31 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-02 מול 2026-09-01 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
   </si>
 </sst>
 </file>
@@ -274,7 +268,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -313,11 +307,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -334,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -342,36 +331,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,80 +723,80 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>7.2</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>7.35</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3">
         <v>0.15</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>5.9</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>6.4</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4">
         <v>0.5</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>19.5</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>20.9</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5">
         <v>1.4</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -848,184 +813,184 @@
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>20.9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>26.9</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>35.9</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>39.9</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8">
         <v>4</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="7" t="s">
+      <c r="G8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>13.07</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>15.48</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9">
         <v>2.41</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="7" t="s">
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>8.2</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>9.5</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10">
         <v>1.3</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>9.9</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>13.9</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11">
         <v>4</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>19.9</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>24.9</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="7" t="s">
+      <c r="G12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>42.9</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>45.9</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13">
         <v>3</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1042,236 +1007,236 @@
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>10.9</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>13.9</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="7" t="s">
+      <c r="G15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>39.9</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>43.9</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16">
         <v>4</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="7" t="s">
+      <c r="G16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>15.9</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <v>17.9</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17">
         <v>2</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="7" t="s">
+      <c r="G17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>18.8</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>19.9</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18">
         <v>1.1</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="7" t="s">
+      <c r="G18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>14.8</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <v>18.9</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19">
         <v>4.1</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="7" t="s">
+      <c r="G19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>19.7</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>24.9</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20">
         <v>5.2</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" t="s">
         <v>56</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" s="7" t="s">
+      <c r="G20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>21.9</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <v>26.9</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21">
         <v>5</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" t="s">
         <v>58</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="7" t="s">
+      <c r="G21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="6">
         <v>22.9</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" t="s">
         <v>60</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" t="s">
         <v>60</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" t="s">
         <v>60</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="3">
         <v>41.5</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4">
         <v>48.9</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23">
         <v>7.4</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" t="s">
         <v>62</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" t="s">
         <v>63</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H23" s="7" t="s">
+      <c r="G23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1288,172 +1253,172 @@
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>15.9</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4">
         <v>19.9</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25">
         <v>4</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" s="7" t="s">
+      <c r="G25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="3">
         <v>4.9</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <v>8.9</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26">
         <v>4</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" t="s">
         <v>25</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="B27" s="3">
+        <v>4.9</v>
+      </c>
+      <c r="C27" s="4">
+        <v>8.9</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="4">
-        <v>4.9</v>
-      </c>
-      <c r="C27" s="5">
-        <v>8.9</v>
-      </c>
-      <c r="D27" s="6">
-        <v>4</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="9" t="s">
+      <c r="B28" s="3">
+        <v>9.9</v>
+      </c>
+      <c r="C28" s="4">
+        <v>12.9</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
         <v>70</v>
       </c>
-      <c r="H27" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="F28" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="4">
-        <v>9.9</v>
-      </c>
-      <c r="C28" s="5">
-        <v>12.9</v>
-      </c>
-      <c r="D28" s="6">
-        <v>3</v>
-      </c>
-      <c r="E28" s="6" t="s">
+      <c r="B29" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="C29" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" t="s">
         <v>72</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="F29" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="4">
-        <v>3.9</v>
-      </c>
-      <c r="C29" s="5">
-        <v>5.9</v>
-      </c>
-      <c r="D29" s="6">
-        <v>2</v>
-      </c>
-      <c r="E29" s="6" t="s">
+      <c r="B30" s="7">
+        <v>406.27</v>
+      </c>
+      <c r="C30" s="7">
+        <v>505.73</v>
+      </c>
+      <c r="D30" s="7">
+        <v>99.46</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
+      <c r="F30" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="11">
-        <v>406.27</v>
-      </c>
-      <c r="C30" s="11">
-        <v>505.73</v>
-      </c>
-      <c r="D30" s="11">
-        <v>99.46</v>
-      </c>
-      <c r="E30" s="11" t="s">
+      <c r="G30" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="78">
   <si>
     <t>מוצר</t>
   </si>
@@ -196,6 +196,9 @@
     <t/>
   </si>
   <si>
+    <t>אין נתון קודם</t>
+  </si>
+  <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
@@ -241,7 +244,7 @@
     <t>אושר עד (99.46 ₪)</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-02 מול 2026-09-01 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-03 מול 2026-09-02 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
   </si>
 </sst>
 </file>
@@ -265,7 +268,7 @@
     </font>
     <font>
       <i/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="9">
@@ -323,20 +326,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -676,11 +700,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="6" width="16" customWidth="1"/>
+    <col min="2" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -723,80 +750,80 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>7.2</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>7.35</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="6">
         <v>0.15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>5.9</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>6.4</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="6">
         <v>0.5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>19.5</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>20.9</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="6">
         <v>1.4</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -813,184 +840,184 @@
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>20.9</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>26.9</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="6">
         <v>6</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>35.9</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>39.9</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="6">
         <v>4</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="G8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>13.07</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>15.48</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="6">
         <v>2.41</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="G9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>8.2</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>9.5</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="6">
         <v>1.3</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="G10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>9.9</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>13.9</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="6">
         <v>4</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="G11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>19.9</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>24.9</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="6">
         <v>5</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="G12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>42.9</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>45.9</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="6">
         <v>3</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="G13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1007,242 +1034,242 @@
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>10.9</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>13.9</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="6">
         <v>3</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="G15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>39.9</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>43.9</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="6">
         <v>4</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="G16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>15.9</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>17.9</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="6">
         <v>2</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="G17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>18.8</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <v>19.9</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="6">
         <v>1.1</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="G18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>14.8</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>18.9</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="6">
         <v>4.1</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="G19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>19.7</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>24.9</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="6">
         <v>5.2</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="G20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>21.9</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>26.9</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="6">
         <v>5</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="G21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="8">
         <v>22.9</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G22" t="s">
-        <v>60</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="G22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="3">
+      <c r="A23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="4">
         <v>41.5</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>48.9</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="6">
         <v>7.4</v>
       </c>
-      <c r="E23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="E23" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="F23" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1253,172 +1280,172 @@
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="3">
+      <c r="A25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="4">
         <v>15.9</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <v>19.9</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="6">
         <v>4</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="G25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="3">
+      <c r="A26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="4">
         <v>4.9</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
         <v>8.9</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="6">
         <v>4</v>
       </c>
-      <c r="E26" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E26" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="G26" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="C27" s="5">
+        <v>8.9</v>
+      </c>
+      <c r="D27" s="6">
+        <v>4</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="C27" s="4">
-        <v>8.9</v>
-      </c>
-      <c r="D27">
-        <v>4</v>
-      </c>
-      <c r="E27" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="F27" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27" s="5" t="s">
+      <c r="G27" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="3">
+      <c r="A28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="4">
         <v>9.9</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <v>12.9</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="6">
         <v>3</v>
       </c>
-      <c r="E28" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E28" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="G28" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="3">
+      <c r="A29" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="4">
         <v>3.9</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>5.9</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="6">
         <v>2</v>
       </c>
-      <c r="E29" t="s">
-        <v>72</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E29" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F29" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="5" t="s">
+      <c r="G29" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="7">
+      <c r="A30" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="10">
         <v>406.27</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="10">
         <v>505.73</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="10">
         <v>99.46</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="7" t="s">
+      <c r="E30" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="F30" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="10" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1426,7 +1453,7 @@
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="80">
   <si>
     <t>מוצר</t>
   </si>
@@ -193,58 +193,64 @@
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
+    <t>34.8%</t>
+  </si>
+  <si>
+    <t>אושר עד (7.96 ₪)</t>
+  </si>
+  <si>
+    <t>⬇ -3.96 ₪</t>
+  </si>
+  <si>
+    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
+  </si>
+  <si>
+    <t>15.1%</t>
+  </si>
+  <si>
+    <t>אושר עד (7.40 ₪)</t>
+  </si>
+  <si>
+    <t>פירות וירקות</t>
+  </si>
+  <si>
+    <t>תפוח עץ פינק ליידי 1 ק"ג</t>
+  </si>
+  <si>
+    <t>עגבניה (ק"ג)</t>
+  </si>
+  <si>
+    <t>44.9%</t>
+  </si>
+  <si>
+    <t>מלפפון (ק"ג)</t>
+  </si>
+  <si>
+    <t>בננות (ק"ג)</t>
+  </si>
+  <si>
+    <t>23.3%</t>
+  </si>
+  <si>
+    <t>בצל יבש (ק"ג)</t>
+  </si>
+  <si>
+    <t>33.9%</t>
+  </si>
+  <si>
+    <t>סה"כ</t>
+  </si>
+  <si>
+    <t>16.7%</t>
+  </si>
+  <si>
+    <t>אושר עד (84.52 ₪)</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>אין נתון קודם</t>
-  </si>
-  <si>
-    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
-  </si>
-  <si>
-    <t>15.1%</t>
-  </si>
-  <si>
-    <t>אושר עד (7.40 ₪)</t>
-  </si>
-  <si>
-    <t>פירות וירקות</t>
-  </si>
-  <si>
-    <t>תפוח עץ פינק ליידי 1 ק"ג</t>
-  </si>
-  <si>
-    <t>עגבניה (ק"ג)</t>
-  </si>
-  <si>
-    <t>44.9%</t>
-  </si>
-  <si>
-    <t>מלפפון (ק"ג)</t>
-  </si>
-  <si>
-    <t>בננות (ק"ג)</t>
-  </si>
-  <si>
-    <t>23.3%</t>
-  </si>
-  <si>
-    <t>בצל יבש (ק"ג)</t>
-  </si>
-  <si>
-    <t>33.9%</t>
-  </si>
-  <si>
-    <t>סה"כ</t>
-  </si>
-  <si>
-    <t>19.7%</t>
-  </si>
-  <si>
-    <t>אושר עד (99.46 ₪)</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-03 מול 2026-09-02 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-04 מול 2026-09-03 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
   </si>
 </sst>
 </file>
@@ -305,7 +311,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -1219,23 +1225,23 @@
       <c r="A22" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="8">
+      <c r="B22" s="4">
+        <v>14.94</v>
+      </c>
+      <c r="C22" s="5">
         <v>22.9</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>60</v>
+      <c r="D22" s="6">
+        <v>7.96</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>60</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="6" t="s">
         <v>61</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>12</v>
@@ -1243,7 +1249,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B23" s="4">
         <v>41.5</v>
@@ -1255,10 +1261,10 @@
         <v>7.4</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>12</v>
@@ -1269,7 +1275,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1281,7 +1287,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B25" s="4">
         <v>15.9</v>
@@ -1307,7 +1313,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="4">
         <v>4.9</v>
@@ -1319,7 +1325,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -1333,7 +1339,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B27" s="4">
         <v>4.9</v>
@@ -1345,7 +1351,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>25</v>
@@ -1359,7 +1365,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B28" s="4">
         <v>9.9</v>
@@ -1371,7 +1377,7 @@
         <v>3</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>39</v>
@@ -1385,7 +1391,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B29" s="4">
         <v>3.9</v>
@@ -1397,7 +1403,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>47</v>
@@ -1411,33 +1417,33 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B30" s="10">
-        <v>406.27</v>
+        <v>421.21</v>
       </c>
       <c r="C30" s="10">
         <v>505.73</v>
       </c>
       <c r="D30" s="10">
-        <v>99.46</v>
+        <v>84.52</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="64">
   <si>
     <t>מוצר</t>
   </si>
@@ -46,7 +46,7 @@
     <t>2.0%</t>
   </si>
   <si>
-    <t>אושר עד (0.15 ₪)</t>
+    <t>אושר עד</t>
   </si>
   <si>
     <t>ללא שינוי</t>
@@ -58,18 +58,12 @@
     <t>7.8%</t>
   </si>
   <si>
-    <t>אושר עד (0.50 ₪)</t>
-  </si>
-  <si>
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
     <t>6.7%</t>
   </si>
   <si>
-    <t>אושר עד (1.40 ₪)</t>
-  </si>
-  <si>
     <t>מאכל ושתיה סגורים</t>
   </si>
   <si>
@@ -79,36 +73,24 @@
     <t>22.3%</t>
   </si>
   <si>
-    <t>אושר עד (6.00 ₪)</t>
-  </si>
-  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
     <t>10.0%</t>
   </si>
   <si>
-    <t>אושר עד (4.00 ₪)</t>
-  </si>
-  <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
     <t>15.6%</t>
   </si>
   <si>
-    <t>אושר עד (2.41 ₪)</t>
-  </si>
-  <si>
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
     <t>13.7%</t>
   </si>
   <si>
-    <t>אושר עד (1.30 ₪)</t>
-  </si>
-  <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
@@ -121,18 +103,12 @@
     <t>20.1%</t>
   </si>
   <si>
-    <t>אושר עד (5.00 ₪)</t>
-  </si>
-  <si>
     <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
     <t>6.5%</t>
   </si>
   <si>
-    <t>אושר עד (3.00 ₪)</t>
-  </si>
-  <si>
     <t>ניקיון וטואלטיקה</t>
   </si>
   <si>
@@ -154,36 +130,24 @@
     <t>11.2%</t>
   </si>
   <si>
-    <t>אושר עד (2.00 ₪)</t>
-  </si>
-  <si>
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
   </si>
   <si>
     <t>5.5%</t>
   </si>
   <si>
-    <t>אושר עד (1.10 ₪)</t>
-  </si>
-  <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
     <t>21.7%</t>
   </si>
   <si>
-    <t>אושר עד (4.10 ₪)</t>
-  </si>
-  <si>
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
     <t>20.9%</t>
   </si>
   <si>
-    <t>אושר עד (5.20 ₪)</t>
-  </si>
-  <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
@@ -196,21 +160,12 @@
     <t>34.8%</t>
   </si>
   <si>
-    <t>אושר עד (7.96 ₪)</t>
-  </si>
-  <si>
-    <t>⬇ -3.96 ₪</t>
-  </si>
-  <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
     <t>15.1%</t>
   </si>
   <si>
-    <t>אושר עד (7.40 ₪)</t>
-  </si>
-  <si>
     <t>פירות וירקות</t>
   </si>
   <si>
@@ -244,13 +199,10 @@
     <t>16.7%</t>
   </si>
   <si>
-    <t>אושר עד (84.52 ₪)</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-04 מול 2026-09-03 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-05 מול 2026-09-04 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
   </si>
 </sst>
 </file>
@@ -277,7 +229,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,11 +263,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -332,38 +279,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -710,11 +637,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="8" width="22" customWidth="1"/>
+    <col min="2" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -756,86 +679,86 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>7.2</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>7.35</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3">
         <v>0.15</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>5.9</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>6.4</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4">
         <v>0.5</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="3">
+        <v>19.5</v>
+      </c>
+      <c r="C5" s="4">
+        <v>20.9</v>
+      </c>
+      <c r="D5">
+        <v>1.4</v>
+      </c>
+      <c r="E5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4">
-        <v>19.5</v>
-      </c>
-      <c r="C5" s="5">
-        <v>20.9</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="7" t="s">
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -846,190 +769,190 @@
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3">
+        <v>20.9</v>
+      </c>
+      <c r="C7" s="4">
+        <v>26.9</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="4">
-        <v>20.9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>26.9</v>
-      </c>
-      <c r="D7" s="6">
-        <v>6</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="B8" s="3">
+        <v>35.9</v>
+      </c>
+      <c r="C8" s="4">
+        <v>39.9</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B9" s="3">
+        <v>13.07</v>
+      </c>
+      <c r="C9" s="4">
+        <v>15.48</v>
+      </c>
+      <c r="D9">
+        <v>2.41</v>
+      </c>
+      <c r="E9" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="4">
-        <v>35.9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>39.9</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>8.2</v>
+      </c>
+      <c r="C10" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="D10">
+        <v>1.3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3">
+        <v>9.9</v>
+      </c>
+      <c r="C11" s="4">
+        <v>13.9</v>
+      </c>
+      <c r="D11">
         <v>4</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="4">
-        <v>13.07</v>
-      </c>
-      <c r="C9" s="5">
-        <v>15.48</v>
-      </c>
-      <c r="D9" s="6">
-        <v>2.41</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="E11" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B12" s="3">
+        <v>19.9</v>
+      </c>
+      <c r="C12" s="4">
+        <v>24.9</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="4">
-        <v>8.2</v>
-      </c>
-      <c r="C10" s="5">
-        <v>9.5</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1.3</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="B13" s="3">
+        <v>42.9</v>
+      </c>
+      <c r="C13" s="4">
+        <v>45.9</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="4">
-        <v>9.9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>13.9</v>
-      </c>
-      <c r="D11" s="6">
-        <v>4</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="4">
-        <v>19.9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>24.9</v>
-      </c>
-      <c r="D12" s="6">
-        <v>5</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="4">
-        <v>42.9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>45.9</v>
-      </c>
-      <c r="D13" s="6">
-        <v>3</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="7" t="s">
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1040,242 +963,242 @@
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3">
+        <v>10.9</v>
+      </c>
+      <c r="C15" s="4">
+        <v>13.9</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3">
+        <v>39.9</v>
+      </c>
+      <c r="C16" s="4">
+        <v>43.9</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="C17" s="4">
+        <v>17.9</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3">
+        <v>18.8</v>
+      </c>
+      <c r="C18" s="4">
+        <v>19.9</v>
+      </c>
+      <c r="D18">
+        <v>1.1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="4">
-        <v>10.9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>13.9</v>
-      </c>
-      <c r="D15" s="6">
-        <v>3</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="B19" s="3">
+        <v>14.8</v>
+      </c>
+      <c r="C19" s="4">
+        <v>18.9</v>
+      </c>
+      <c r="D19">
+        <v>4.1</v>
+      </c>
+      <c r="E19" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="4">
-        <v>39.9</v>
-      </c>
-      <c r="C16" s="5">
-        <v>43.9</v>
-      </c>
-      <c r="D16" s="6">
-        <v>4</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="B20" s="3">
+        <v>19.7</v>
+      </c>
+      <c r="C20" s="4">
+        <v>24.9</v>
+      </c>
+      <c r="D20">
+        <v>5.2</v>
+      </c>
+      <c r="E20" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="4">
-        <v>15.9</v>
-      </c>
-      <c r="C17" s="5">
-        <v>17.9</v>
-      </c>
-      <c r="D17" s="6">
-        <v>2</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="B21" s="3">
+        <v>21.9</v>
+      </c>
+      <c r="C21" s="4">
+        <v>26.9</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="B22" s="3">
+        <v>14.94</v>
+      </c>
+      <c r="C22" s="4">
+        <v>22.9</v>
+      </c>
+      <c r="D22">
+        <v>7.96</v>
+      </c>
+      <c r="E22" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="4">
-        <v>18.8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>19.9</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1.1</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="B23" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="C23" s="4">
+        <v>48.9</v>
+      </c>
+      <c r="D23">
+        <v>7.4</v>
+      </c>
+      <c r="E23" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="4">
-        <v>14.8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>18.9</v>
-      </c>
-      <c r="D19" s="6">
-        <v>4.1</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="4">
-        <v>19.7</v>
-      </c>
-      <c r="C20" s="5">
-        <v>24.9</v>
-      </c>
-      <c r="D20" s="6">
-        <v>5.2</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="4">
-        <v>21.9</v>
-      </c>
-      <c r="C21" s="5">
-        <v>26.9</v>
-      </c>
-      <c r="D21" s="6">
-        <v>5</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="4">
-        <v>14.94</v>
-      </c>
-      <c r="C22" s="5">
-        <v>22.9</v>
-      </c>
-      <c r="D22" s="6">
-        <v>7.96</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="4">
-        <v>41.5</v>
-      </c>
-      <c r="C23" s="5">
-        <v>48.9</v>
-      </c>
-      <c r="D23" s="6">
-        <v>7.4</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H23" s="7" t="s">
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1286,172 +1209,172 @@
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="4">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="3">
         <v>15.9</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4">
         <v>19.9</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25">
         <v>4</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" s="7" t="s">
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B26" s="4">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="3">
         <v>4.9</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <v>8.9</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26">
         <v>4</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" s="7" t="s">
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="4">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="3">
         <v>4.9</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4">
         <v>8.9</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27">
         <v>4</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27" s="7" t="s">
+      <c r="E27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="4">
+      <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="3">
         <v>9.9</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <v>12.9</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28">
         <v>3</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="7" t="s">
+      <c r="E28" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="4">
+      <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="3">
         <v>3.9</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="4">
         <v>5.9</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29">
         <v>2</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="7" t="s">
+      <c r="E29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="10">
+      <c r="A30" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="6">
         <v>421.21</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="6">
         <v>505.73</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="6">
         <v>84.52</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>78</v>
+      <c r="E30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
+      <c r="A31" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="73">
   <si>
     <t>מוצר</t>
   </si>
@@ -19,9 +19,15 @@
     <t>מחיר אושר עד</t>
   </si>
   <si>
+    <t>מבצע אושר עד</t>
+  </si>
+  <si>
     <t>מחיר שופרסל</t>
   </si>
   <si>
+    <t>מבצע שופרסל</t>
+  </si>
+  <si>
     <t>הפרש ₪</t>
   </si>
   <si>
@@ -43,6 +49,9 @@
     <t>חלב 3% תנובה 1 ליטר</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>אושר עד</t>
   </si>
   <si>
@@ -61,6 +70,9 @@
     <t>טונה סטארקיסט בשמן 4X160 גרם</t>
   </si>
   <si>
+    <t>23.00 (2 ב-46)</t>
+  </si>
+  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
@@ -76,30 +88,63 @@
     <t>יין סגל אדום יבש 750 מ"ל</t>
   </si>
   <si>
+    <t>22.50 (2 ב-45)</t>
+  </si>
+  <si>
     <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
+    <t>37.50 (2 ב-75)</t>
+  </si>
+  <si>
+    <t>40.00 (2 ב-80)</t>
+  </si>
+  <si>
     <t>שיבולת שועל קוואקר 500 גרם</t>
   </si>
   <si>
+    <t>9.00 (2 ב-18)</t>
+  </si>
+  <si>
+    <t>11.00 (2 ב-22)</t>
+  </si>
+  <si>
     <t>אין נתון קודם</t>
   </si>
   <si>
     <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
   </si>
   <si>
+    <t>15.90</t>
+  </si>
+  <si>
     <t>ספגטי אסם 500 גרם</t>
   </si>
   <si>
+    <t>6.00 (4 ב-24)</t>
+  </si>
+  <si>
     <t>פסטה פנה ריגטה ברילה 500 גרם</t>
   </si>
   <si>
+    <t>6.50 (2 ב-13)</t>
+  </si>
+  <si>
+    <t>7.50 (2 ב-15)</t>
+  </si>
+  <si>
     <t>דבש טבעי עמק חפר 350 גרם</t>
   </si>
   <si>
+    <t>14.90</t>
+  </si>
+  <si>
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
+    <t>18.00 (2 ב-36)</t>
+  </si>
+  <si>
     <t>ניקיון וטואלטיקה</t>
   </si>
   <si>
@@ -115,21 +160,45 @@
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
   </si>
   <si>
+    <t>12.00 (2 ב-24)</t>
+  </si>
+  <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
+    <t>7.40</t>
+  </si>
+  <si>
+    <t>16.90</t>
+  </si>
+  <si>
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
+    <t>15.00 (2 ב-30)</t>
+  </si>
+  <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
+    <t>22.00 (2 ב-44)</t>
+  </si>
+  <si>
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
+    <t>11.94</t>
+  </si>
+  <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
+    <t>29.90</t>
+  </si>
+  <si>
+    <t>33.33 (3 ב-100)</t>
+  </si>
+  <si>
     <t>פירות וירקות</t>
   </si>
   <si>
@@ -148,13 +217,19 @@
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
+    <t>3.90</t>
+  </si>
+  <si>
+    <t>⬆ +1.00 ₪</t>
+  </si>
+  <si>
     <t>סה"כ</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-06 מול 2026-09-05 -- אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-06 מול 2026-09-05 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -162,7 +237,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -184,7 +259,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,6 +293,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -234,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -246,18 +331,29 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,18 +694,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="8" width="22" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -634,10 +732,16 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -646,88 +750,108 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="4">
         <v>7.2</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="6">
         <v>7.35</v>
       </c>
-      <c r="D3" s="6">
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="7">
         <v>0.15</v>
       </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G3" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4">
         <v>5.9</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6">
         <v>6.4</v>
       </c>
-      <c r="D4" s="6">
+      <c r="E4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="7">
         <v>0.5</v>
       </c>
-      <c r="E4" s="7">
-        <v>7.8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G4" s="8">
+        <v>0.078</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" s="4">
         <v>19.5</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6">
         <v>20.9</v>
       </c>
-      <c r="D5" s="6">
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="7">
         <v>1.4</v>
       </c>
-      <c r="E5" s="7">
-        <v>6.7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G5" s="8">
+        <v>0.067</v>
+      </c>
+      <c r="H5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -736,348 +860,428 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" s="4">
         <v>20.9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="6">
         <v>26.9</v>
       </c>
-      <c r="D7" s="6">
+      <c r="E7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="7">
         <v>6</v>
       </c>
-      <c r="E7" s="7">
-        <v>22.3</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G7" s="8">
+        <v>0.223</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B8" s="4">
         <v>35.9</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="6">
         <v>39.9</v>
       </c>
-      <c r="D8" s="6">
+      <c r="E8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="7">
         <v>4</v>
       </c>
-      <c r="E8" s="7">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G8" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B9" s="4">
         <v>13.07</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6">
         <v>15.48</v>
       </c>
-      <c r="D9" s="6">
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7">
         <v>2.41</v>
       </c>
-      <c r="E9" s="7">
-        <v>15.6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G9" s="8">
+        <v>0.156</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B10" s="4">
         <v>8.2</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="6">
         <v>9.5</v>
       </c>
-      <c r="D10" s="6">
+      <c r="E10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="7">
         <v>1.3</v>
       </c>
-      <c r="E10" s="7">
-        <v>13.7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G10" s="8">
+        <v>0.13699999999999998</v>
+      </c>
+      <c r="H10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B11" s="4">
         <v>9.9</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="6">
         <v>13.9</v>
       </c>
-      <c r="D11" s="6">
+      <c r="E11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7">
         <v>4</v>
       </c>
-      <c r="E11" s="7">
-        <v>28.8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G11" s="8">
+        <v>0.28800000000000003</v>
+      </c>
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B12" s="4">
         <v>19.9</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6">
         <v>24.9</v>
       </c>
-      <c r="D12" s="6">
+      <c r="E12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="7">
         <v>5</v>
       </c>
-      <c r="E12" s="7">
-        <v>20.1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G12" s="8">
+        <v>0.201</v>
+      </c>
+      <c r="H12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B13" s="4">
         <v>42.9</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="6">
         <v>45.9</v>
       </c>
-      <c r="D13" s="6">
+      <c r="E13" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="7">
         <v>3</v>
       </c>
-      <c r="E13" s="7">
-        <v>6.5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G13" s="8">
+        <v>0.065</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B14" s="4">
         <v>11.9</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="6">
         <v>14.9</v>
       </c>
-      <c r="D14" s="6">
+      <c r="E14" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="7">
         <v>3</v>
       </c>
-      <c r="E14" s="7">
-        <v>20.1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>23</v>
+      <c r="G14" s="8">
+        <v>0.201</v>
       </c>
       <c r="H14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B15" s="4">
         <v>13.9</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="6">
         <v>16.9</v>
       </c>
-      <c r="D15" s="6">
+      <c r="E15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="7">
         <v>3</v>
       </c>
-      <c r="E15" s="7">
-        <v>17.8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" t="s">
-        <v>23</v>
+      <c r="G15" s="8">
+        <v>0.17800000000000002</v>
       </c>
       <c r="H15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B16" s="4">
         <v>4.9</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6">
         <v>7.9</v>
       </c>
-      <c r="D16" s="6">
+      <c r="E16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="7">
         <v>3</v>
       </c>
-      <c r="E16" s="7">
-        <v>38</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
-        <v>23</v>
+      <c r="G16" s="8">
+        <v>0.38</v>
       </c>
       <c r="H16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B17" s="4">
         <v>7.9</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="6">
         <v>9.9</v>
       </c>
-      <c r="D17" s="6">
+      <c r="E17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="7">
         <v>2</v>
       </c>
-      <c r="E17" s="7">
-        <v>20.2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" t="s">
-        <v>23</v>
+      <c r="G17" s="8">
+        <v>0.20199999999999999</v>
       </c>
       <c r="H17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B18" s="4">
         <v>8.9</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="6">
         <v>16.9</v>
       </c>
-      <c r="D18" s="6">
+      <c r="E18" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="7">
         <v>8</v>
       </c>
-      <c r="E18" s="7">
-        <v>47.3</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" t="s">
-        <v>23</v>
+      <c r="G18" s="8">
+        <v>0.473</v>
       </c>
       <c r="H18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B19" s="4">
         <v>9.9</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="6">
         <v>22.9</v>
       </c>
-      <c r="D19" s="6">
-        <v>13</v>
-      </c>
-      <c r="E19" s="7">
-        <v>56.8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" t="s">
-        <v>23</v>
+      <c r="E19" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="7">
+        <v>13</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.568</v>
       </c>
       <c r="H19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1086,244 +1290,300 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B21" s="4">
         <v>10.9</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="6">
         <v>13.9</v>
       </c>
-      <c r="D21" s="6">
+      <c r="E21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="7">
         <v>3</v>
       </c>
-      <c r="E21" s="7">
-        <v>21.6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G21" s="8">
+        <v>0.21600000000000003</v>
+      </c>
+      <c r="H21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B22" s="4">
         <v>39.9</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="6">
         <v>43.9</v>
       </c>
-      <c r="D22" s="6">
+      <c r="E22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="7">
         <v>4</v>
       </c>
-      <c r="E22" s="7">
-        <v>9.1</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G22" s="8">
+        <v>0.091</v>
+      </c>
+      <c r="H22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B23" s="4">
         <v>15.9</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="6">
         <v>17.9</v>
       </c>
-      <c r="D23" s="6">
+      <c r="E23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="7">
         <v>2</v>
       </c>
-      <c r="E23" s="7">
-        <v>11.2</v>
-      </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G23" s="8">
+        <v>0.11199999999999999</v>
+      </c>
+      <c r="H23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B24" s="4">
         <v>18.8</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="6">
         <v>19.9</v>
       </c>
-      <c r="D24" s="6">
+      <c r="E24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="7">
         <v>1.1</v>
       </c>
-      <c r="E24" s="7">
-        <v>5.5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G24" s="8">
+        <v>0.055</v>
+      </c>
+      <c r="H24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B25" s="4">
         <v>14.8</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="6">
         <v>18.9</v>
       </c>
-      <c r="D25" s="6">
+      <c r="E25" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="7">
         <v>4.1</v>
       </c>
-      <c r="E25" s="7">
-        <v>21.7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G25" s="8">
+        <v>0.217</v>
+      </c>
+      <c r="H25" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B26" s="4">
         <v>19.7</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="6">
         <v>24.9</v>
       </c>
-      <c r="D26" s="6">
+      <c r="E26" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="7">
         <v>5.2</v>
       </c>
-      <c r="E26" s="7">
-        <v>20.9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G26" s="8">
+        <v>0.209</v>
+      </c>
+      <c r="H26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B27" s="4">
         <v>21.9</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="6">
         <v>26.9</v>
       </c>
-      <c r="D27" s="6">
+      <c r="E27" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="7">
         <v>5</v>
       </c>
-      <c r="E27" s="7">
-        <v>18.6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G27" s="8">
+        <v>0.18600000000000003</v>
+      </c>
+      <c r="H27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B28" s="4">
         <v>14.94</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="6">
         <v>22.9</v>
       </c>
-      <c r="D28" s="6">
+      <c r="E28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="7">
         <v>7.96</v>
       </c>
-      <c r="E28" s="7">
-        <v>34.8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G28" s="8">
+        <v>0.348</v>
+      </c>
+      <c r="H28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B29" s="4">
         <v>41.5</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="6">
         <v>48.9</v>
       </c>
-      <c r="D29" s="6">
+      <c r="E29" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="7">
         <v>7.4</v>
       </c>
-      <c r="E29" s="7">
-        <v>15.1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G29" s="8">
+        <v>0.151</v>
+      </c>
+      <c r="H29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1332,182 +1592,222 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="B31" s="4">
         <v>15.9</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="6">
         <v>19.9</v>
       </c>
-      <c r="D31" s="6">
+      <c r="E31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="7">
         <v>4</v>
       </c>
-      <c r="E31" s="7">
-        <v>20.1</v>
-      </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G31" s="8">
+        <v>0.201</v>
+      </c>
+      <c r="H31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="B32" s="4">
         <v>4.9</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="6">
         <v>8.9</v>
       </c>
-      <c r="D32" s="6">
+      <c r="E32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="7">
         <v>4</v>
       </c>
-      <c r="E32" s="7">
-        <v>44.9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G32" s="8">
+        <v>0.449</v>
+      </c>
+      <c r="H32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="B33" s="4">
         <v>4.9</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="6">
         <v>8.9</v>
       </c>
-      <c r="D33" s="6">
+      <c r="E33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="7">
         <v>4</v>
       </c>
-      <c r="E33" s="7">
-        <v>44.9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G33" s="8">
+        <v>0.449</v>
+      </c>
+      <c r="H33" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="B34" s="4">
         <v>9.9</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="6">
         <v>12.9</v>
       </c>
-      <c r="D34" s="6">
+      <c r="E34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="7">
         <v>3</v>
       </c>
-      <c r="E34" s="7">
-        <v>23.3</v>
-      </c>
-      <c r="F34" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G34" s="8">
+        <v>0.233</v>
+      </c>
+      <c r="H34" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="B35" s="4">
-        <v>3.9</v>
-      </c>
-      <c r="C35" s="5">
+        <v>4.9</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="6">
         <v>5.9</v>
       </c>
-      <c r="D35" s="6">
-        <v>2</v>
-      </c>
-      <c r="E35" s="7">
-        <v>33.9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="10">
-        <v>478.61</v>
-      </c>
-      <c r="C36" s="10">
+      <c r="E35" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0.16899999999999998</v>
+      </c>
+      <c r="H35" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="13">
+        <v>479.61</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="13">
         <v>595.13</v>
       </c>
-      <c r="D36" s="10">
-        <v>116.52</v>
-      </c>
-      <c r="E36" s="11">
-        <v>19.6</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
+      <c r="E36" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" s="13">
+        <v>115.52</v>
+      </c>
+      <c r="G36" s="15">
+        <v>0.194</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A37:J37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="70">
+  <si>
+    <t>מעקב מחירים יומי - 2026-09-07</t>
+  </si>
   <si>
     <t>מוצר</t>
   </si>
@@ -109,9 +112,6 @@
     <t>11.00 (2 ב-22)</t>
   </si>
   <si>
-    <t>אין נתון קודם</t>
-  </si>
-  <si>
     <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
   </si>
   <si>
@@ -187,7 +187,7 @@
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
-    <t>11.94</t>
+    <t>19.90</t>
   </si>
   <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
@@ -196,9 +196,6 @@
     <t>29.90</t>
   </si>
   <si>
-    <t>33.33 (3 ב-100)</t>
-  </si>
-  <si>
     <t>פירות וירקות</t>
   </si>
   <si>
@@ -217,19 +214,13 @@
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
-    <t>3.90</t>
-  </si>
-  <si>
-    <t>⬆ +1.00 ₪</t>
-  </si>
-  <si>
     <t>סה"כ</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-06 מול 2026-09-05 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-07 מול 2026-09-06 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -239,13 +230,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <b/>
@@ -259,7 +255,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -298,11 +294,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -324,35 +315,35 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -694,1120 +685,1132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5">
         <v>7.2</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7">
         <v>7.35</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="8">
         <v>0.15</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G4" s="9">
         <v>0.02</v>
       </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="H4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="5">
         <v>5.9</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7">
         <v>6.4</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="8">
         <v>0.5</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G5" s="9">
         <v>0.078</v>
       </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="H5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5">
         <v>19.5</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="7">
         <v>20.9</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="8">
         <v>1.4</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G6" s="9">
         <v>0.067</v>
       </c>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="H6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="5">
         <v>20.9</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="8">
         <v>6</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G8" s="9">
         <v>0.223</v>
       </c>
-      <c r="H7" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="4">
+      <c r="H8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="5">
         <v>35.9</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7">
         <v>39.9</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
         <v>4</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G9" s="9">
         <v>0.1</v>
       </c>
-      <c r="H8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="4">
+      <c r="H9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="5">
         <v>13.07</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="7">
         <v>15.48</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="8">
         <v>2.41</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G10" s="9">
         <v>0.156</v>
       </c>
-      <c r="H9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="4">
+      <c r="H10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="5">
         <v>8.2</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="7">
         <v>9.5</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="8">
         <v>1.3</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G11" s="9">
         <v>0.13699999999999998</v>
       </c>
-      <c r="H10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="4">
+      <c r="H11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="5">
         <v>9.9</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="7">
         <v>13.9</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="8">
         <v>4</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G12" s="9">
         <v>0.28800000000000003</v>
       </c>
-      <c r="H11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="4">
+      <c r="H12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="5">
         <v>19.9</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="7">
         <v>24.9</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E13" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="8">
         <v>5</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G13" s="9">
         <v>0.201</v>
       </c>
-      <c r="H12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="4">
+      <c r="H13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C14" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="8">
         <v>3</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G14" s="9">
         <v>0.065</v>
       </c>
-      <c r="H13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="4">
+      <c r="H14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="7">
+      <c r="E15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G15" s="9">
         <v>0.201</v>
       </c>
-      <c r="H14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="H15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B16" s="5">
         <v>13.9</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="7">
         <v>16.9</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E16" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F16" s="8">
         <v>3</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G16" s="9">
         <v>0.17800000000000002</v>
       </c>
-      <c r="H15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="H16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B17" s="5">
         <v>4.9</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E17" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F17" s="8">
         <v>3</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G17" s="9">
         <v>0.38</v>
       </c>
-      <c r="H16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="H17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D18" s="7">
         <v>9.9</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G18" s="9">
         <v>0.20199999999999999</v>
       </c>
-      <c r="H17" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="H18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B19" s="5">
         <v>8.9</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F19" s="8">
         <v>8</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G19" s="9">
         <v>0.473</v>
       </c>
-      <c r="H18" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="H19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B20" s="5">
         <v>9.9</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="7">
         <v>22.9</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E20" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="7">
-        <v>13</v>
-      </c>
-      <c r="G19" s="8">
+      <c r="F20" s="8">
+        <v>13</v>
+      </c>
+      <c r="G20" s="9">
         <v>0.568</v>
       </c>
-      <c r="H19" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="H20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B22" s="5">
         <v>10.9</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="7">
         <v>13.9</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="7">
+      <c r="E22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="8">
         <v>3</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G22" s="9">
         <v>0.21600000000000003</v>
       </c>
-      <c r="H21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="H22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B23" s="5">
         <v>39.9</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="7">
         <v>43.9</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="E23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G23" s="9">
         <v>0.091</v>
       </c>
-      <c r="H22" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="H23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B24" s="5">
         <v>15.9</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="7">
         <v>17.9</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="E24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G24" s="9">
         <v>0.11199999999999999</v>
       </c>
-      <c r="H23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="H24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C25" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D25" s="7">
         <v>19.9</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="E25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="8">
         <v>1.1</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G25" s="9">
         <v>0.055</v>
       </c>
-      <c r="H24" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="H25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B26" s="5">
         <v>14.8</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C26" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E26" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F26" s="8">
         <v>4.1</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G26" s="9">
         <v>0.217</v>
       </c>
-      <c r="H25" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="H26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D27" s="7">
         <v>24.9</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="E27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="8">
         <v>5.2</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G27" s="9">
         <v>0.209</v>
       </c>
-      <c r="H26" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="H27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B28" s="5">
         <v>21.9</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C28" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F28" s="8">
         <v>5</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G28" s="9">
         <v>0.18600000000000003</v>
       </c>
-      <c r="H27" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="H28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B29" s="5">
         <v>14.94</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C29" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="8">
         <v>7.96</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G29" s="9">
         <v>0.348</v>
       </c>
-      <c r="H28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="H29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C30" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="E30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="8">
         <v>7.4</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G30" s="9">
         <v>0.151</v>
       </c>
-      <c r="H29" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
+      <c r="H30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="5">
+        <v>15.9</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="7">
+        <v>19.9</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="8">
+        <v>4</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0.201</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="4">
-        <v>15.9</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="6">
-        <v>19.9</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="7">
+      <c r="B33" s="5">
+        <v>4.9</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="7">
+        <v>8.9</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="8">
         <v>4</v>
       </c>
-      <c r="G31" s="8">
-        <v>0.201</v>
-      </c>
-      <c r="H31" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="G33" s="9">
+        <v>0.449</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B34" s="5">
         <v>4.9</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="7">
         <v>8.9</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="7">
+      <c r="E34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="8">
         <v>4</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G34" s="9">
         <v>0.449</v>
       </c>
-      <c r="H32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="H34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B35" s="5">
+        <v>9.9</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="7">
+        <v>12.9</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="8">
+        <v>3</v>
+      </c>
+      <c r="G35" s="9">
+        <v>0.233</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="5">
         <v>4.9</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="6">
-        <v>8.9</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="7">
-        <v>4</v>
-      </c>
-      <c r="G33" s="8">
-        <v>0.449</v>
-      </c>
-      <c r="H33" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="4">
-        <v>9.9</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="6">
-        <v>12.9</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="7">
-        <v>3</v>
-      </c>
-      <c r="G34" s="8">
-        <v>0.233</v>
-      </c>
-      <c r="H34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="C36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="7">
+        <v>5.9</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="8">
+        <v>1</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0.16899999999999998</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="4">
-        <v>4.9</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="6">
-        <v>5.9</v>
-      </c>
-      <c r="E35" s="10" t="s">
+      <c r="B37" s="13">
+        <v>479.61</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="7">
-        <v>1</v>
-      </c>
-      <c r="G35" s="8">
-        <v>0.16899999999999998</v>
-      </c>
-      <c r="H35" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="11" t="s">
+      <c r="D37" s="13">
+        <v>595.13</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F37" s="13">
+        <v>115.52</v>
+      </c>
+      <c r="G37" s="15">
+        <v>0.19399999999999998</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="J35" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="13">
-        <v>479.61</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" s="13">
-        <v>595.13</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="F36" s="13">
-        <v>115.52</v>
-      </c>
-      <c r="G36" s="15">
-        <v>0.194</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A37:J37"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A38:J38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="98">
   <si>
-    <t>מעקב מחירים יומי — 2026-09-09</t>
+    <t>מעקב מחירים יומי — 2026-09-10</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -304,14 +304,14 @@
     <t>17.9%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-09 מול 2026-09-08 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-10 מול 2026-09-09 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -331,7 +331,6 @@
     <font>
       <b/>
     </font>
-    <font/>
     <font>
       <i/>
       <sz val="9"/>
@@ -392,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -409,7 +408,7 @@
     <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -418,10 +417,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -436,7 +432,7 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -791,7 +787,7 @@
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -805,7 +801,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -837,7 +833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -870,16 +866,16 @@
       <c r="F4" s="8">
         <v>0.15</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="10" t="s">
+      <c r="H4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -902,16 +898,16 @@
       <c r="F5" s="8">
         <v>0.5</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="10" t="s">
+      <c r="H5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -934,20 +930,20 @@
       <c r="F6" s="8">
         <v>1.4</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
@@ -974,22 +970,22 @@
       <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="10" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="8">
         <v>6</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="10" t="s">
+      <c r="H8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1012,16 +1008,16 @@
       <c r="F9" s="8">
         <v>4</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="10" t="s">
+      <c r="H9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1044,16 +1040,16 @@
       <c r="F10" s="8">
         <v>2.41</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="10" t="s">
+      <c r="H10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1076,16 +1072,16 @@
       <c r="F11" s="8">
         <v>1.3</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="10" t="s">
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1108,16 +1104,16 @@
       <c r="F12" s="8">
         <v>4</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="10" t="s">
+      <c r="H12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1134,22 +1130,22 @@
       <c r="D13" s="7">
         <v>24.9</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="10" t="s">
         <v>34</v>
       </c>
       <c r="F13" s="8">
         <v>5</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="10" t="s">
+      <c r="H13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1160,28 +1156,28 @@
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="10" t="s">
         <v>38</v>
       </c>
       <c r="F14" s="8">
         <v>3</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="10" t="s">
+      <c r="H14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1192,28 +1188,28 @@
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="10" t="s">
+      <c r="H15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1230,22 +1226,22 @@
       <c r="D16" s="7">
         <v>16.9</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="8">
         <v>3</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="10" t="s">
+      <c r="H16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1262,22 +1258,22 @@
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="10" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="8">
         <v>3</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="10" t="s">
+      <c r="H17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1288,28 +1284,28 @@
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="7">
         <v>9.9</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="10" t="s">
         <v>51</v>
       </c>
       <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="10" t="s">
+      <c r="H18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1326,22 +1322,22 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="10" t="s">
         <v>54</v>
       </c>
       <c r="F19" s="8">
         <v>8</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="10" t="s">
+      <c r="H19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1352,32 +1348,32 @@
       <c r="B20" s="5">
         <v>18.9</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D20" s="7">
         <v>22.9</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="10" t="s">
         <v>58</v>
       </c>
       <c r="F20" s="8">
         <v>4</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>60</v>
       </c>
@@ -1410,16 +1406,16 @@
       <c r="F22" s="8">
         <v>3</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H22" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="10" t="s">
+      <c r="H22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1442,16 +1438,16 @@
       <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="H23" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="10" t="s">
+      <c r="H23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1474,16 +1470,16 @@
       <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="H24" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="10" t="s">
+      <c r="H24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1494,7 +1490,7 @@
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>68</v>
       </c>
       <c r="D25" s="7">
@@ -1506,16 +1502,16 @@
       <c r="F25" s="8">
         <v>1.1</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H25" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="10" t="s">
+      <c r="H25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1526,28 +1522,28 @@
       <c r="B26" s="5">
         <v>14.8</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="10" t="s">
         <v>72</v>
       </c>
       <c r="F26" s="8">
         <v>4.1</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="H26" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="10" t="s">
+      <c r="H26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1558,7 +1554,7 @@
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="7">
@@ -1570,16 +1566,16 @@
       <c r="F27" s="8">
         <v>5.2</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="10" t="s">
+      <c r="H27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1590,28 +1586,28 @@
       <c r="B28" s="5">
         <v>21.9</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F28" s="8">
         <v>5</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="10" t="s">
+      <c r="H28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1622,7 +1618,7 @@
       <c r="B29" s="5">
         <v>14.94</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D29" s="7">
@@ -1634,16 +1630,16 @@
       <c r="F29" s="8">
         <v>7.96</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="H29" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="10" t="s">
+      <c r="H29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1654,32 +1650,32 @@
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="10" t="s">
         <v>84</v>
       </c>
       <c r="F30" s="8">
         <v>7.4</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="H30" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>86</v>
       </c>
@@ -1712,16 +1708,16 @@
       <c r="F32" s="8">
         <v>4</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H32" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="10" t="s">
+      <c r="H32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1744,16 +1740,16 @@
       <c r="F33" s="8">
         <v>4</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="10" t="s">
+      <c r="H33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1776,16 +1772,16 @@
       <c r="F34" s="8">
         <v>4</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="H34" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="10" t="s">
+      <c r="H34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1808,16 +1804,16 @@
       <c r="F35" s="8">
         <v>3</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="H35" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="10" t="s">
+      <c r="H35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1840,54 +1836,54 @@
       <c r="F36" s="8">
         <v>1</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="H36" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="10" t="s">
+      <c r="H36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="12">
         <v>488.61</v>
       </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="13">
+      <c r="C37" s="13"/>
+      <c r="D37" s="12">
         <v>595.13</v>
       </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="13">
+      <c r="E37" s="13"/>
+      <c r="F37" s="12">
         <v>106.52</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="G37" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="98">
-  <si>
-    <t>מעקב מחירים יומי — 2026-09-10</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="99">
+  <si>
+    <t>מעקב מחירים יומי — 2026-09-11</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -301,10 +301,13 @@
     <t>סה"כ</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>17.9%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-10 מול 2026-09-09 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-11 מול 2026-09-10 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -391,13 +394,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -405,16 +408,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -426,12 +426,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -787,7 +785,7 @@
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,7 +799,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -863,7 +861,7 @@
       <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="6">
         <v>0.15</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -872,10 +870,10 @@
       <c r="H4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="9" t="s">
+      <c r="I4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -895,7 +893,7 @@
       <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="6">
         <v>0.5</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -904,10 +902,10 @@
       <c r="H5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="I5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -927,7 +925,7 @@
       <c r="E6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>1.4</v>
       </c>
       <c r="G6" s="6" t="s">
@@ -936,10 +934,10 @@
       <c r="H6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="9" t="s">
+      <c r="I6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -970,10 +968,10 @@
       <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <v>6</v>
       </c>
       <c r="G8" s="6" t="s">
@@ -982,10 +980,10 @@
       <c r="H8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="9" t="s">
+      <c r="I8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1005,7 +1003,7 @@
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -1014,10 +1012,10 @@
       <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="I9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1037,7 +1035,7 @@
       <c r="E10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="6">
         <v>2.41</v>
       </c>
       <c r="G10" s="6" t="s">
@@ -1046,10 +1044,10 @@
       <c r="H10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="9" t="s">
+      <c r="I10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1069,7 +1067,7 @@
       <c r="E11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="6">
         <v>1.3</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -1078,10 +1076,10 @@
       <c r="H11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="9" t="s">
+      <c r="I11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1101,7 +1099,7 @@
       <c r="E12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="6">
         <v>4</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -1110,10 +1108,10 @@
       <c r="H12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="I12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1130,10 +1128,10 @@
       <c r="D13" s="7">
         <v>24.9</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="6">
         <v>5</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -1142,10 +1140,10 @@
       <c r="H13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="9" t="s">
+      <c r="I13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1156,16 +1154,16 @@
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="6">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -1174,10 +1172,10 @@
       <c r="H14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="9" t="s">
+      <c r="I14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1188,16 +1186,16 @@
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="6">
         <v>3</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -1206,10 +1204,10 @@
       <c r="H15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="9" t="s">
+      <c r="I15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1226,10 +1224,10 @@
       <c r="D16" s="7">
         <v>16.9</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="6">
         <v>3</v>
       </c>
       <c r="G16" s="6" t="s">
@@ -1238,10 +1236,10 @@
       <c r="H16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="9" t="s">
+      <c r="I16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1258,10 +1256,10 @@
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="6">
         <v>3</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -1270,10 +1268,10 @@
       <c r="H17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="9" t="s">
+      <c r="I17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1284,16 +1282,16 @@
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="7">
         <v>9.9</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="6">
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -1302,10 +1300,10 @@
       <c r="H18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="9" t="s">
+      <c r="I18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1322,10 +1320,10 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="6">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -1334,10 +1332,10 @@
       <c r="H19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="9" t="s">
+      <c r="I19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1348,16 +1346,16 @@
       <c r="B20" s="5">
         <v>18.9</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D20" s="7">
         <v>22.9</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="6">
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -1366,10 +1364,10 @@
       <c r="H20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="9" t="s">
+      <c r="I20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1403,7 +1401,7 @@
       <c r="E22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="6">
         <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -1412,10 +1410,10 @@
       <c r="H22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="9" t="s">
+      <c r="I22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1435,7 +1433,7 @@
       <c r="E23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="6">
         <v>4</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -1444,10 +1442,10 @@
       <c r="H23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="9" t="s">
+      <c r="I23" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1467,7 +1465,7 @@
       <c r="E24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="6">
         <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
@@ -1476,10 +1474,10 @@
       <c r="H24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="9" t="s">
+      <c r="I24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1490,7 +1488,7 @@
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>68</v>
       </c>
       <c r="D25" s="7">
@@ -1499,7 +1497,7 @@
       <c r="E25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="6">
         <v>1.1</v>
       </c>
       <c r="G25" s="6" t="s">
@@ -1508,10 +1506,10 @@
       <c r="H25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="9" t="s">
+      <c r="I25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1522,16 +1520,16 @@
       <c r="B26" s="5">
         <v>14.8</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="6">
         <v>4.1</v>
       </c>
       <c r="G26" s="6" t="s">
@@ -1540,10 +1538,10 @@
       <c r="H26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="9" t="s">
+      <c r="I26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1554,7 +1552,7 @@
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="7">
@@ -1563,7 +1561,7 @@
       <c r="E27" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="6">
         <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -1572,10 +1570,10 @@
       <c r="H27" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="9" t="s">
+      <c r="I27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1586,16 +1584,16 @@
       <c r="B28" s="5">
         <v>21.9</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>54</v>
       </c>
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="6">
         <v>5</v>
       </c>
       <c r="G28" s="6" t="s">
@@ -1604,10 +1602,10 @@
       <c r="H28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I28" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="9" t="s">
+      <c r="I28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1618,7 +1616,7 @@
       <c r="B29" s="5">
         <v>14.94</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D29" s="7">
@@ -1627,7 +1625,7 @@
       <c r="E29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="6">
         <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
@@ -1636,10 +1634,10 @@
       <c r="H29" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="9" t="s">
+      <c r="I29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1650,16 +1648,16 @@
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="6">
         <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
@@ -1668,10 +1666,10 @@
       <c r="H30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="9" t="s">
+      <c r="I30" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1705,7 +1703,7 @@
       <c r="E32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="6">
         <v>4</v>
       </c>
       <c r="G32" s="6" t="s">
@@ -1714,10 +1712,10 @@
       <c r="H32" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="9" t="s">
+      <c r="I32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1737,7 +1735,7 @@
       <c r="E33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="6">
         <v>4</v>
       </c>
       <c r="G33" s="6" t="s">
@@ -1746,10 +1744,10 @@
       <c r="H33" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="9" t="s">
+      <c r="I33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1769,7 +1767,7 @@
       <c r="E34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="6">
         <v>4</v>
       </c>
       <c r="G34" s="6" t="s">
@@ -1778,10 +1776,10 @@
       <c r="H34" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="9" t="s">
+      <c r="I34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1801,7 +1799,7 @@
       <c r="E35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="6">
         <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
@@ -1810,10 +1808,10 @@
       <c r="H35" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="9" t="s">
+      <c r="I35" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1833,7 +1831,7 @@
       <c r="E36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="6">
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
@@ -1842,48 +1840,58 @@
       <c r="H36" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="9" t="s">
+      <c r="I36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="11">
         <v>488.61</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="12">
+      <c r="C37" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" s="11">
         <v>595.13</v>
       </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="12">
+      <c r="E37" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F37" s="11">
         <v>106.52</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="J37" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="99">
   <si>
-    <t>מעקב מחירים יומי — 2026-09-11</t>
+    <t>מעקב מחירי סופרמרקט - 2026-09-12</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -307,7 +307,7 @@
     <t>17.9%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-11 מול 2026-09-10 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-12 מול 2026-09-11 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -394,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -408,13 +408,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -426,10 +425,12 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -775,17 +776,18 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -799,7 +801,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -861,7 +863,7 @@
       <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="8">
         <v>0.15</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -870,10 +872,10 @@
       <c r="H4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -893,7 +895,7 @@
       <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="8">
         <v>0.5</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -902,10 +904,10 @@
       <c r="H5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -925,7 +927,7 @@
       <c r="E6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="8">
         <v>1.4</v>
       </c>
       <c r="G6" s="6" t="s">
@@ -934,10 +936,10 @@
       <c r="H6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="8" t="s">
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -968,10 +970,10 @@
       <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="8">
         <v>6</v>
       </c>
       <c r="G8" s="6" t="s">
@@ -980,10 +982,10 @@
       <c r="H8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1003,7 +1005,7 @@
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="8">
         <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -1012,10 +1014,10 @@
       <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1035,7 +1037,7 @@
       <c r="E10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="8">
         <v>2.41</v>
       </c>
       <c r="G10" s="6" t="s">
@@ -1044,10 +1046,10 @@
       <c r="H10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1067,7 +1069,7 @@
       <c r="E11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="8">
         <v>1.3</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -1076,10 +1078,10 @@
       <c r="H11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1099,7 +1101,7 @@
       <c r="E12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="8">
         <v>4</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -1108,10 +1110,10 @@
       <c r="H12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1128,10 +1130,10 @@
       <c r="D13" s="7">
         <v>24.9</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="8">
         <v>5</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -1140,10 +1142,10 @@
       <c r="H13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1154,16 +1156,16 @@
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="8">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -1172,10 +1174,10 @@
       <c r="H14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="8" t="s">
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1186,16 +1188,16 @@
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="8">
         <v>3</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -1204,10 +1206,10 @@
       <c r="H15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1224,10 +1226,10 @@
       <c r="D16" s="7">
         <v>16.9</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="8">
         <v>3</v>
       </c>
       <c r="G16" s="6" t="s">
@@ -1236,10 +1238,10 @@
       <c r="H16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1256,10 +1258,10 @@
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="8">
         <v>3</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -1268,10 +1270,10 @@
       <c r="H17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1282,16 +1284,16 @@
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="7">
         <v>9.9</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="8">
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -1300,10 +1302,10 @@
       <c r="H18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="8" t="s">
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1320,10 +1322,10 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="8">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -1332,10 +1334,10 @@
       <c r="H19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="8" t="s">
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1346,16 +1348,16 @@
       <c r="B20" s="5">
         <v>18.9</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D20" s="7">
         <v>22.9</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="8">
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -1364,10 +1366,10 @@
       <c r="H20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="8" t="s">
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1401,7 +1403,7 @@
       <c r="E22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="8">
         <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -1410,10 +1412,10 @@
       <c r="H22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="8" t="s">
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1433,7 +1435,7 @@
       <c r="E23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="8">
         <v>4</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -1442,10 +1444,10 @@
       <c r="H23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="8" t="s">
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1465,7 +1467,7 @@
       <c r="E24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="8">
         <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
@@ -1474,10 +1476,10 @@
       <c r="H24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="8" t="s">
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1488,7 +1490,7 @@
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="10" t="s">
         <v>68</v>
       </c>
       <c r="D25" s="7">
@@ -1497,7 +1499,7 @@
       <c r="E25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="8">
         <v>1.1</v>
       </c>
       <c r="G25" s="6" t="s">
@@ -1506,10 +1508,10 @@
       <c r="H25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="8" t="s">
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1520,16 +1522,16 @@
       <c r="B26" s="5">
         <v>14.8</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="8">
         <v>4.1</v>
       </c>
       <c r="G26" s="6" t="s">
@@ -1538,10 +1540,10 @@
       <c r="H26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="8" t="s">
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1552,7 +1554,7 @@
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="10" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="7">
@@ -1561,7 +1563,7 @@
       <c r="E27" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="8">
         <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -1570,10 +1572,10 @@
       <c r="H27" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="8" t="s">
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1584,16 +1586,16 @@
       <c r="B28" s="5">
         <v>21.9</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="10" t="s">
         <v>54</v>
       </c>
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="8">
         <v>5</v>
       </c>
       <c r="G28" s="6" t="s">
@@ -1602,10 +1604,10 @@
       <c r="H28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="8" t="s">
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1616,7 +1618,7 @@
       <c r="B29" s="5">
         <v>14.94</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D29" s="7">
@@ -1625,7 +1627,7 @@
       <c r="E29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="8">
         <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
@@ -1634,10 +1636,10 @@
       <c r="H29" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1648,16 +1650,16 @@
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="10" t="s">
         <v>83</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="8">
         <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
@@ -1666,10 +1668,10 @@
       <c r="H30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1703,7 +1705,7 @@
       <c r="E32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="8">
         <v>4</v>
       </c>
       <c r="G32" s="6" t="s">
@@ -1712,10 +1714,10 @@
       <c r="H32" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="8" t="s">
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1735,7 +1737,7 @@
       <c r="E33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="8">
         <v>4</v>
       </c>
       <c r="G33" s="6" t="s">
@@ -1744,10 +1746,10 @@
       <c r="H33" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="8" t="s">
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1767,7 +1769,7 @@
       <c r="E34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="8">
         <v>4</v>
       </c>
       <c r="G34" s="6" t="s">
@@ -1776,10 +1778,10 @@
       <c r="H34" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I34" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="8" t="s">
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1799,7 +1801,7 @@
       <c r="E35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="8">
         <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
@@ -1808,10 +1810,10 @@
       <c r="H35" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="8" t="s">
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1831,7 +1833,7 @@
       <c r="E36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="8">
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
@@ -1840,58 +1842,58 @@
       <c r="H36" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="8" t="s">
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="12">
         <v>488.61</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="12">
         <v>595.13</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="12">
         <v>106.52</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="H37" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="12" t="s">
+      <c r="H37" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="J37" s="12" t="s">
+      <c r="J37" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">
